--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Leyenda" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendientes!$A$4:$L$94</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Pendientes!$A$4:$L$108</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="906" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="526">
   <si>
     <t xml:space="preserve">Resumen de pendientes</t>
   </si>
@@ -385,13 +385,67 @@
     <t xml:space="preserve">Móvil</t>
   </si>
   <si>
-    <t xml:space="preserve">App compañera en Flutter para el tendero (venta con escáner nativo, consulta de inventario, notificaciones)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan 07 completo. No hay código Flutter en el repositorio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimado del plan: 2 a 3 semanas.</t>
+    <t xml:space="preserve">App nativa del Tendero en Flutter: vender (con fiado), caja con egresos, recibir mercancía, alertas y catálogo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan 07, sección 6 (3-oct). Repositorio aparte; la construye el equipo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versión de prueba para Android en la visita (semana del 5-oct); piloto con la versión corregida.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backend para la app: sesión por canal (web y app a la vez), Ventas.canal y docs/contrato_api_app_tendero.md con prueba por endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan 07, sección 6.3; plan 22, sección 5 (A.1). Rama feat/backend-app-tendero.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antes de la visita.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guion de la fase 4 (tareas, medidas, cuestionario), autorización de datos y formato de línea base para la visita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan 22, sección 5 (A.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decidir si se mantiene despierto Render en horario de tienda con un ping (plan gratuito: se duerme tras 15 min y tarda ~1 min en volver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisión pendiente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan 22, sección 5 (C.5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mientras tanto, abrir la app unos minutos antes de entrar a cada tienda.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distribución en iPhone (requiere Mac y membresía de pago de Apple para TestFlight)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan 07, sección 6.3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Después del piloto.</t>
   </si>
   <si>
     <t xml:space="preserve">P08-01</t>
@@ -865,16 +919,19 @@
     <t xml:space="preserve">utils/backup.js y cron de las 2:00 en schedulerService.js.</t>
   </si>
   <si>
+    <t xml:space="preserve">Solo sirve en local: en Render gratuito el disco es temporal y el servidor se duerme. Desde el 3-oct no se programa en producción; lo reemplaza el workflow de GitHub Actions.</t>
+  </si>
+  <si>
     <t xml:space="preserve">P19-02</t>
   </si>
   <si>
     <t xml:space="preserve">Copia de los respaldos en almacenamiento externo, verificar que pg_dump exista en Render y probar una restauración</t>
   </si>
   <si>
-    <t xml:space="preserve">Plan 19, sección 3.1. Los respaldos quedan en el disco temporal de Render.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Requisito antes de recibir datos de tiendas reales (piloto, fase 5).</t>
+    <t xml:space="preserve">.github/workflows/respaldo-neon.yml (diario, cifrado con gpg, 14 días de retención, postgres:18) y docs/restaurar_respaldo.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauración verificada el 3-oct, según Luis.</t>
   </si>
   <si>
     <t xml:space="preserve">P19-03</t>
@@ -925,7 +982,7 @@
     <t xml:space="preserve">Plan 19, sección 3.4.</t>
   </si>
   <si>
-    <t xml:space="preserve">Llevar el prototipo a la prueba de usabilidad (fase 4). Decisión pendiente: si el colaborador puede cambiar su propio modo.</t>
+    <t xml:space="preserve">Después del piloto: la app nativa del Tendero (plan 07, sección 6) cubre esas vistas. Solo si el piloto muestra que hace falta.</t>
   </si>
   <si>
     <t xml:space="preserve">P19-07</t>
@@ -934,9 +991,6 @@
     <t xml:space="preserve">Modo básico, fases D y E: permisos del colaborador sobre órdenes y catálogo simplificado</t>
   </si>
   <si>
-    <t xml:space="preserve">Hacerlo solo si la prueba de usabilidad confirma que el modo básico ayuda. Decisión pendiente: si el colaborador ve montos o solo cantidades.</t>
-  </si>
-  <si>
     <t xml:space="preserve">P19-08</t>
   </si>
   <si>
@@ -1042,10 +1096,7 @@
     <t xml:space="preserve">R0: pruebas de caracterización de IA, proveedores, autenticación y productos</t>
   </si>
   <si>
-    <t xml:space="preserve">Rama test/plan21-r0-caracterizacion (5 commits): 48 pruebas nuevas en 5 archivos. Integración 95/95 en 5 corridas seguidas (97/97 con la guardia de limitadores); unitarias 196/196. Cobertura combinada de sentencias: 34,9 % → 55,8 %.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hecho en la rama; falta la revisión de Luis y el merge a main. Requisito para las demás fases del plan 21.</t>
+    <t xml:space="preserve">Mezclada en main y subida el 28-sep (merge 2e523dc): 48 pruebas de caracterización y 2 de guardia. Cobertura combinada ≈35 % → ≈56 % (npm run test:coverage:combinada).</t>
   </si>
   <si>
     <t xml:space="preserve">P21-02</t>
@@ -1057,6 +1108,9 @@
     <t xml:space="preserve">Plan 21, sección 4.</t>
   </si>
   <si>
+    <t xml:space="preserve">Después del piloto, salvo que la fecha del Sprint 6.3 lo exija antes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">P21-03</t>
   </si>
   <si>
@@ -1069,6 +1123,9 @@
     <t xml:space="preserve">R3: hooks y descomposición del frontend, empezando por DashboardPage</t>
   </si>
   <si>
+    <t xml:space="preserve">Después del piloto: con la app nativa ya no hace falta adelantar R3.1.</t>
+  </si>
+  <si>
     <t xml:space="preserve">P21-05</t>
   </si>
   <si>
@@ -1084,12 +1141,12 @@
     <t xml:space="preserve">Decidir el transporte de las alertas en tiempo real: SSE (recomendado) o Socket.io</t>
   </si>
   <si>
-    <t xml:space="preserve">Decisión pendiente</t>
-  </si>
-  <si>
     <t xml:space="preserve">Plan 21, secciones 5.2 y 8.</t>
   </si>
   <si>
+    <t xml:space="preserve">Replantear después del piloto: para la app nativa, notificaciones push; SSE para la web.</t>
+  </si>
+  <si>
     <t xml:space="preserve">P21-07</t>
   </si>
   <si>
@@ -1099,6 +1156,9 @@
     <t xml:space="preserve">Plan 21, sección 5.3.</t>
   </si>
   <si>
+    <t xml:space="preserve">Después del piloto, replanteado (ver la fila de la decisión de transporte).</t>
+  </si>
+  <si>
     <t xml:space="preserve">P21-08</t>
   </si>
   <si>
@@ -1117,7 +1177,7 @@
     <t xml:space="preserve">routes/authRoutes.js:25; app.js solo limita forgot-password y reset-password. Caracterizado en autenticacion_flujos.test.js (R0).</t>
   </si>
   <si>
-    <t xml:space="preserve">Encontrado en R0; corregir fuera de la refactorización.</t>
+    <t xml:space="preserve">En la rama feat/backend-app-tendero, antes de la visita.</t>
   </si>
   <si>
     <t xml:space="preserve">P21-10</t>
@@ -1141,7 +1201,7 @@
     <t xml:space="preserve">Medido sin reinicio: global 242/600 sobre user_1, auth 7/10. tests/integration/helpers/limitadores.js reinicia los MemoryStore al comienzo de cada archivo (pico por archivo: 48/600 y 5/10); guardia limitadores_reinicio.test.js.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hecho en la rama del R0, solo en pruebas; se cierra con el merge.</t>
+    <t xml:space="preserve">Mezclado en main con R0 el 28-sep.</t>
   </si>
   <si>
     <t xml:space="preserve">P21-12</t>
@@ -1165,7 +1225,7 @@
     <t xml:space="preserve">middleware/rateLimiter.js (skip con req.path.startsWith('/api/login')…); comprobado con una prueba temporal del agente.</t>
   </si>
   <si>
-    <t xml:space="preserve">Decidir si se corrige el prefijo o se elimina el skip.</t>
+    <t xml:space="preserve">En la rama feat/backend-app-tendero, junto con P21-09.</t>
   </si>
   <si>
     <t xml:space="preserve">P21-14</t>
@@ -1177,7 +1237,7 @@
     <t xml:space="preserve">Plan 21, punto 2.4 y sección 6; plan 22, sección 5 (A.3).</t>
   </si>
   <si>
-    <t xml:space="preserve">Una doble apertura dañaría los arqueos del piloto. Commit aparte con su prueba.</t>
+    <t xml:space="preserve">En la rama feat/backend-app-tendero, antes de la visita: la app abre y cierra caja.</t>
   </si>
   <si>
     <t xml:space="preserve">P21-15</t>
@@ -1192,16 +1252,28 @@
     <t xml:space="preserve">Recomendado: sí, antes de tener datos reales en producción.</t>
   </si>
   <si>
+    <t xml:space="preserve">P21-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 de los 11 E2E de Playwright fallan también en main: quedaron desalineados con el frontend actual (selector de rol en el login, #store_name, ToastContext)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">docs/hallazgo_e2e_desactualizados.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Después del piloto, antes de R3. Mientras tanto, los cambios de interfaz se verifican a mano.</t>
+  </si>
+  <si>
     <t xml:space="preserve">P22-01</t>
   </si>
   <si>
-    <t xml:space="preserve">I0: auditoría de autorización: matriz rol × endpoint, requireAdmin donde corresponda y pruebas de 403 para el Tendero (empieza por las rutas de tienda)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan 22, sección 1.4. Rama fix/rutas-tienda-requireadmin (solo rutas de tienda). Comportamiento actual registrado en autorizacion_roles.test.js (plan 21, R0).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La rama de tienda espera aprobación; falta el resto de la matriz (ver P22-09 y P22-10). Hacer antes que el resto del plan.</t>
+    <t xml:space="preserve">I0: auditoría de autorización: matriz rol × endpoint, requireAdmin donde corresponda y pruebas de 403 para el Tendero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramas fix/rutas-tienda-requireadmin (28-sep) y fix/i0-matriz-roles (3-oct), mezcladas y subidas. requireAdmin en 16 rutas más las de tienda; interfaz del Tendero ajustada (escáner solo suma stock).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verificación manual en producción por el QA del equipo con un usuario Tendero.</t>
   </si>
   <si>
     <t xml:space="preserve">P22-02</t>
@@ -1216,7 +1288,7 @@
     <t xml:space="preserve">Plan 22, secciones 3.1 y 3.2.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antes de la convocatoria pública.</t>
+    <t xml:space="preserve">Antes del arranque del piloto (plan 22, sección 5, C.2).</t>
   </si>
   <si>
     <t xml:space="preserve">P22-03</t>
@@ -1228,7 +1300,7 @@
     <t xml:space="preserve">Plan 22, secciones 3.3 y 3.5.</t>
   </si>
   <si>
-    <t xml:space="preserve">Es el instrumento para medir la activación y la adopción del piloto.</t>
+    <t xml:space="preserve">Antes del arranque del piloto. Debe excluir las tiendas de prueba (P22-19).</t>
   </si>
   <si>
     <t xml:space="preserve">P22-04</t>
@@ -1243,7 +1315,7 @@
     <t xml:space="preserve">Plan 22, sección 3.4.</t>
   </si>
   <si>
-    <t xml:space="preserve">Junto con el modo básico A y B (plan 19, 3.4).</t>
+    <t xml:space="preserve">Después del piloto: con la app nativa, el modo básico web deja de ir antes.</t>
   </si>
   <si>
     <t xml:space="preserve">P22-05</t>
@@ -1255,7 +1327,7 @@
     <t xml:space="preserve">Plan 22, secciones 3.5 y 3.7; plan 19, 3.5.</t>
   </si>
   <si>
-    <t xml:space="preserve">Antes de publicar la convocatoria.</t>
+    <t xml:space="preserve">Antes del arranque del piloto.</t>
   </si>
   <si>
     <t xml:space="preserve">P22-06</t>
@@ -1294,7 +1366,7 @@
     <t xml:space="preserve">Plan 22, sección 5.</t>
   </si>
   <si>
-    <t xml:space="preserve">Si la app cambia a mitad del piloto, no se puede atribuir un cambio en los indicadores.</t>
+    <t xml:space="preserve">Incluye la app: durante el piloto no se publican versiones nuevas, salvo correcciones de errores.</t>
   </si>
   <si>
     <t xml:space="preserve">P22-09</t>
@@ -1306,7 +1378,7 @@
     <t xml:space="preserve">routes/cashRegisterRoutes.js:15-16; models/CashRegister.js approveExpense y rejectExpense (WHERE id_egreso = ? sin id_tienda). Caracterizado en autorizacion_roles.test.js.</t>
   </si>
   <si>
-    <t xml:space="preserve">El hallazgo más grave: rompe el aislamiento entre tiendas. Primero dentro de I0.</t>
+    <t xml:space="preserve">Corregido el 28-sep: solo el Administrador, solo de su tienda y solo desde el estado Registrado (409 en otro caso).</t>
   </si>
   <si>
     <t xml:space="preserve">P22-10</t>
@@ -1318,7 +1390,97 @@
     <t xml:space="preserve">Plan 22, sección 1.4; tabla de autorizacion_roles.test.js.</t>
   </si>
   <si>
-    <t xml:space="preserve">No todo es un defecto: resolver una alerta o registrar un conteo físico pueden ser tareas del Tendero. Las pruebas que hoy esperan 200 se invierten a 403 solo donde se decida.</t>
+    <t xml:space="preserve">Decidido el 28-sep: D1 a D4 = solo Administrador (plan 22, sección 7, decisión 6; docs/propuesta_matriz_roles_P22-10.md).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POST /api/admin/seed vaciaba todas las tablas de todas las tiendas y creaba admin/admin123; cualquier persona registrada podía llamarla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregido el 28-sep (fix/seed-produccion): ruta eliminada; la semilla solo corre como comando con guardia de base local.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan 22, sección 1.4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1: reportes editables y borrables entre tiendas (Report.update/delete filtraban solo por id)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregido el 28-sep (fix/aislamiento-reportes-feedback).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2: evaluación de IA de órdenes de otra tienda, con fuga de nombres y ventas de productos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregido el 28-sep (fix/aislamiento-reportes-feedback); evaluateOrder caracterizado antes del cambio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3: POST /api/alertas/test-summary enviaba correos sin requireAdmin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregido el 28-sep.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4: un token CSRF inválido responde 500 en vez de 403 (el manejador global ignora err.status)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">app.js, manejador global de errores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisar antes cómo reacciona la interfaz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5: clienteRoutes aplica requireLogin a todo /api (rutas inexistentes responden 401 en vez de 404)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">routes/clienteRoutes.js.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6: la carpeta exports/ era compartida; cualquier usuario listaba y descargaba exportaciones de otras tiendas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corregido el 3-oct (fix/exports-por-tienda): tienda en el nombre, verificación al descargar, borrado tras descarga, sin listado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7: PUT /api/productos/agregar/:id sumaba o restaba stock sin movimiento en el Kardex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruta eliminada el 3-oct (fix/i0-matriz-roles).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excluir las tiendas de prueba del equipo de las métricas del piloto (propuesta: Tienda.es_prueba)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan 22, sección 3.3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antes del arranque del piloto, junto con I2.</t>
   </si>
   <si>
     <t xml:space="preserve">Bitácora de cambios</t>
@@ -1370,6 +1532,30 @@
   </si>
   <si>
     <t xml:space="preserve">R0 del plan 21 terminado en la rama test/plan21-r0-caracterizacion (48 pruebas, sin cambios de producción, sin merge). I0 pasa a En progreso y se amplía a auditoría de autorización. Se agregan los hallazgos de R0: egresos entre tiendas, verify-reset-code sin limitador, recepción sin tope, contadores compartidos en las pruebas (resuelto en la rama), código muerto en bulkUpload y skip inerte de globalLimiter.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P21-01, P21-11, P22-09, P22-10 y hallazgos de I0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Por verificar / No iniciado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezclados y subidos el 28-sep: R0, P22-09 con regla de estados, rutas de tienda, eliminación de la semilla en producción y C1 a C3. Matriz de roles decidida (D1 a D4 = solo Administrador).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P22-01, C6, C7, P19 (respaldos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En progreso / No iniciado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mezclados y subidos el 3-oct: C6, I0 completo (incluye C7) y respaldo externo en GitHub Actions (postgres:18). Restauración verificada, según Luis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P07, P19 (modo básico), P21-R1/R3/T, P22-I3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La app nativa del Tendero se adelanta para la visita a las tiendas piloto (semana del 5-oct). Repositorio aparte, Android primero. Nuevo orden en el plan 22, sección 5.</t>
   </si>
   <si>
     <t xml:space="preserve">Cómo usar este archivo</t>
@@ -2313,12 +2499,12 @@
         <v>11</v>
       </c>
       <c r="B5" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$F$5:$F$294,A5)</f>
-        <v>62</v>
+        <f aca="false">COUNTIF(Pendientes!$F$5:$F$308,A5)</f>
+        <v>66</v>
       </c>
       <c r="C5" s="6" t="n">
         <f aca="false">IF($B$12=0,0,B5/$B$12)</f>
-        <v>0.688888888888889</v>
+        <v>0.634615384615385</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>12</v>
@@ -2327,19 +2513,19 @@
         <v>13</v>
       </c>
       <c r="G5" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E5,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E5,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E5,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E5,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H5" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E5,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E5,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E5,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E5,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E5)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E5)</f>
         <v>1</v>
       </c>
     </row>
@@ -2348,12 +2534,12 @@
         <v>14</v>
       </c>
       <c r="B6" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$F$5:$F$294,A6)</f>
+        <f aca="false">COUNTIF(Pendientes!$F$5:$F$308,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
         <f aca="false">IF($B$12=0,0,B6/$B$12)</f>
-        <v>0.0111111111111111</v>
+        <v>0.00961538461538462</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>15</v>
@@ -2362,19 +2548,19 @@
         <v>16</v>
       </c>
       <c r="G6" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E6,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E6,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E6,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E6,Pendientes!$F$5:$F$308,"")</f>
         <v>4</v>
       </c>
       <c r="H6" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E6,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E6,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I6" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E6,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E6,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E6)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E6)</f>
         <v>5</v>
       </c>
     </row>
@@ -2383,12 +2569,12 @@
         <v>17</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$F$5:$F$294,A7)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(Pendientes!$F$5:$F$308,A7)</f>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
         <f aca="false">IF($B$12=0,0,B7/$B$12)</f>
-        <v>0.0555555555555556</v>
+        <v>0.0576923076923077</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>18</v>
@@ -2397,19 +2583,19 @@
         <v>19</v>
       </c>
       <c r="G7" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E7,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E7,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E7,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E7,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H7" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E7,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E7,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E7,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E7,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E7)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E7)</f>
         <v>1</v>
       </c>
     </row>
@@ -2418,12 +2604,12 @@
         <v>20</v>
       </c>
       <c r="B8" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$F$5:$F$294,A8)</f>
-        <v>13</v>
+        <f aca="false">COUNTIF(Pendientes!$F$5:$F$308,A8)</f>
+        <v>24</v>
       </c>
       <c r="C8" s="6" t="n">
         <f aca="false">IF($B$12=0,0,B8/$B$12)</f>
-        <v>0.144444444444444</v>
+        <v>0.230769230769231</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>21</v>
@@ -2432,19 +2618,19 @@
         <v>22</v>
       </c>
       <c r="G8" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E8,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E8,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E8,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E8,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H8" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E8,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E8,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I8" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E8,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E8,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E8)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E8)</f>
         <v>2</v>
       </c>
     </row>
@@ -2453,7 +2639,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$F$5:$F$294,A9)</f>
+        <f aca="false">COUNTIF(Pendientes!$F$5:$F$308,A9)</f>
         <v>0</v>
       </c>
       <c r="C9" s="6" t="n">
@@ -2467,20 +2653,20 @@
         <v>25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E9,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E9,Pendientes!$F$5:$F$294,"")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E9,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E9,Pendientes!$F$5:$F$308,"")</f>
+        <v>5</v>
       </c>
       <c r="H9" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E9,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E9,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I9" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E9,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E9,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J9" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E9)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E9)</f>
+        <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2488,12 +2674,12 @@
         <v>26</v>
       </c>
       <c r="B10" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$F$5:$F$294,A10)</f>
+        <f aca="false">COUNTIF(Pendientes!$F$5:$F$308,A10)</f>
         <v>3</v>
       </c>
       <c r="C10" s="6" t="n">
         <f aca="false">IF($B$12=0,0,B10/$B$12)</f>
-        <v>0.0333333333333333</v>
+        <v>0.0288461538461538</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>27</v>
@@ -2502,19 +2688,19 @@
         <v>28</v>
       </c>
       <c r="G10" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E10,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E10,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E10,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E10,Pendientes!$F$5:$F$308,"")</f>
         <v>7</v>
       </c>
       <c r="H10" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E10,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E10,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>2</v>
       </c>
       <c r="I10" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E10,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E10,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J10" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E10)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E10)</f>
         <v>9</v>
       </c>
     </row>
@@ -2523,12 +2709,12 @@
         <v>29</v>
       </c>
       <c r="B11" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$F$5:$F$294,A11)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF(Pendientes!$F$5:$F$308,A11)</f>
+        <v>4</v>
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">IF($B$12=0,0,B11/$B$12)</f>
-        <v>0.0666666666666667</v>
+        <v>0.0384615384615385</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>30</v>
@@ -2537,19 +2723,19 @@
         <v>31</v>
       </c>
       <c r="G11" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E11,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E11,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E11,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E11,Pendientes!$F$5:$F$308,"")</f>
         <v>6</v>
       </c>
       <c r="H11" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E11,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E11,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I11" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E11,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E11,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J11" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E11)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E11)</f>
         <v>6</v>
       </c>
     </row>
@@ -2559,7 +2745,7 @@
       </c>
       <c r="B12" s="14" t="n">
         <f aca="false">SUM(B5:B11)</f>
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>32</v>
@@ -2568,19 +2754,19 @@
         <v>33</v>
       </c>
       <c r="G12" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E12,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E12,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E12,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E12,Pendientes!$F$5:$F$308,"")</f>
         <v>4</v>
       </c>
       <c r="H12" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E12,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E12,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E12,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E12,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J12" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E12)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E12)</f>
         <v>4</v>
       </c>
     </row>
@@ -2590,7 +2776,7 @@
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">B12-B8-B10</f>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>35</v>
@@ -2599,19 +2785,19 @@
         <v>36</v>
       </c>
       <c r="G13" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E13,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E13,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E13,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E13,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H13" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E13,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E13,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I13" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E13,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E13,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J13" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E13)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E13)</f>
         <v>2</v>
       </c>
     </row>
@@ -2620,8 +2806,8 @@
         <v>37</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$G$5:$G$294,"Alta",Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")</f>
-        <v>16</v>
+        <f aca="false">COUNTIFS(Pendientes!$G$5:$G$308,"Alta",Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")</f>
+        <v>15</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>38</v>
@@ -2630,19 +2816,19 @@
         <v>39</v>
       </c>
       <c r="G14" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E14,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E14,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E14,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E14,Pendientes!$F$5:$F$308,"")</f>
         <v>3</v>
       </c>
       <c r="H14" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E14,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E14,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I14" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E14,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E14,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J14" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E14)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E14)</f>
         <v>4</v>
       </c>
     </row>
@@ -2654,19 +2840,19 @@
         <v>41</v>
       </c>
       <c r="G15" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E15,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E15,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E15,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E15,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H15" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E15,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E15,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I15" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E15,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E15,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J15" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E15)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E15)</f>
         <v>1</v>
       </c>
     </row>
@@ -2681,19 +2867,19 @@
         <v>44</v>
       </c>
       <c r="G16" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E16,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E16,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E16,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E16,Pendientes!$F$5:$F$308,"")</f>
         <v>2</v>
       </c>
       <c r="H16" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E16,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E16,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I16" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E16,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E16,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>1</v>
       </c>
       <c r="J16" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E16)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E16)</f>
         <v>4</v>
       </c>
     </row>
@@ -2705,19 +2891,19 @@
         <v>46</v>
       </c>
       <c r="G17" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E17,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E17,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E17,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E17,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H17" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E17,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E17,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I17" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E17,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E17,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J17" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E17)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E17)</f>
         <v>2</v>
       </c>
     </row>
@@ -2729,19 +2915,19 @@
         <v>48</v>
       </c>
       <c r="G18" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E18,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E18,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E18,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E18,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H18" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E18,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E18,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I18" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E18,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E18,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>1</v>
       </c>
       <c r="J18" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E18)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E18)</f>
         <v>2</v>
       </c>
     </row>
@@ -2753,19 +2939,19 @@
         <v>50</v>
       </c>
       <c r="G19" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E19,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E19,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E19,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E19,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H19" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E19,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E19,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I19" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E19,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E19,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>1</v>
       </c>
       <c r="J19" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E19)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E19)</f>
         <v>3</v>
       </c>
     </row>
@@ -2777,19 +2963,19 @@
         <v>52</v>
       </c>
       <c r="G20" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E20,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E20,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E20,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E20,Pendientes!$F$5:$F$308,"")</f>
         <v>1</v>
       </c>
       <c r="H20" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E20,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E20,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I20" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E20,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E20,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J20" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E20)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E20)</f>
         <v>2</v>
       </c>
     </row>
@@ -2801,19 +2987,19 @@
         <v>54</v>
       </c>
       <c r="G21" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E21,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E21,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E21,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E21,Pendientes!$F$5:$F$308,"")</f>
         <v>9</v>
       </c>
       <c r="H21" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E21,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E21,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>1</v>
       </c>
       <c r="I21" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E21,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E21,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E21)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E21)</f>
         <v>10</v>
       </c>
     </row>
@@ -2825,19 +3011,19 @@
         <v>56</v>
       </c>
       <c r="G22" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E22,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E22,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E22,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E22,Pendientes!$F$5:$F$308,"")</f>
         <v>6</v>
       </c>
       <c r="H22" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E22,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E22,Pendientes!$F$5:$F$308,"Terminado")</f>
         <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E22,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E22,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J22" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E22)</f>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E22)</f>
         <v>6</v>
       </c>
     </row>
@@ -2849,20 +3035,20 @@
         <v>58</v>
       </c>
       <c r="G23" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E23,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E23,Pendientes!$F$5:$F$294,"")</f>
-        <v>15</v>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E23,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E23,Pendientes!$F$5:$F$308,"")</f>
+        <v>14</v>
       </c>
       <c r="H23" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E23,Pendientes!$F$5:$F$294,"Terminado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E23,Pendientes!$F$5:$F$308,"Terminado")</f>
+        <v>2</v>
+      </c>
+      <c r="I23" s="5" t="n">
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E23,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E23,Pendientes!$F$5:$F$294,"Descartado")</f>
-        <v>0</v>
-      </c>
       <c r="J23" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E23)</f>
-        <v>15</v>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E23)</f>
+        <v>16</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2873,20 +3059,20 @@
         <v>60</v>
       </c>
       <c r="G24" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E24,Pendientes!$F$5:$F$294,"&lt;&gt;Terminado",Pendientes!$F$5:$F$294,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$294,E24,Pendientes!$F$5:$F$294,"")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E24,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E24,Pendientes!$F$5:$F$308,"")</f>
         <v>8</v>
       </c>
       <c r="H24" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E24,Pendientes!$F$5:$F$294,"Terminado")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E24,Pendientes!$F$5:$F$308,"Terminado")</f>
+        <v>11</v>
       </c>
       <c r="I24" s="5" t="n">
-        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$294,E24,Pendientes!$F$5:$F$294,"Descartado")</f>
+        <f aca="false">COUNTIFS(Pendientes!$B$5:$B$308,E24,Pendientes!$F$5:$F$308,"Descartado")</f>
         <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <f aca="false">COUNTIF(Pendientes!$B$5:$B$294,E24)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF(Pendientes!$B$5:$B$308,E24)</f>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -2911,7 +3097,7 @@
     <tabColor rgb="FF252C93"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -3021,7 +3207,7 @@
       </c>
       <c r="L5" s="22" t="n">
         <f aca="true">IF(K5="","",TODAY()-K5)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3056,7 +3242,7 @@
       </c>
       <c r="L6" s="22" t="n">
         <f aca="true">IF(K6="","",TODAY()-K6)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3093,7 +3279,7 @@
       </c>
       <c r="L7" s="22" t="n">
         <f aca="true">IF(K7="","",TODAY()-K7)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3130,7 +3316,7 @@
       </c>
       <c r="L8" s="22" t="n">
         <f aca="true">IF(K8="","",TODAY()-K8)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3165,7 +3351,7 @@
       </c>
       <c r="L9" s="22" t="n">
         <f aca="true">IF(K9="","",TODAY()-K9)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3202,7 +3388,7 @@
       </c>
       <c r="L10" s="22" t="n">
         <f aca="true">IF(K10="","",TODAY()-K10)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3239,7 +3425,7 @@
       </c>
       <c r="L11" s="22" t="n">
         <f aca="true">IF(K11="","",TODAY()-K11)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3274,7 +3460,7 @@
       </c>
       <c r="L12" s="22" t="n">
         <f aca="true">IF(K12="","",TODAY()-K12)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3309,7 +3495,7 @@
       </c>
       <c r="L13" s="22" t="n">
         <f aca="true">IF(K13="","",TODAY()-K13)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3326,13 +3512,13 @@
         <v>119</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H14" s="19" t="s">
         <v>120</v>
@@ -3346,7 +3532,7 @@
       </c>
       <c r="L14" s="22" t="n">
         <f aca="true">IF(K14="","",TODAY()-K14)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3354,7 +3540,7 @@
         <v>122</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C15" s="19" t="s">
         <v>123</v>
@@ -3366,7 +3552,7 @@
         <v>83</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G15" s="19" t="s">
         <v>77</v>
@@ -3374,113 +3560,119 @@
       <c r="H15" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="I15" s="19"/>
+      <c r="I15" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="J15" s="19"/>
       <c r="K15" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L15" s="22" t="n">
         <f aca="true">IF(K15="","",TODAY()-K15)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E16" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="I16" s="19"/>
+        <v>130</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>126</v>
+      </c>
       <c r="J16" s="19"/>
       <c r="K16" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L16" s="22" t="n">
         <f aca="true">IF(K16="","",TODAY()-K16)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="D17" s="19" t="s">
         <v>132</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G17" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>133</v>
-      </c>
-      <c r="I17" s="19"/>
+        <v>134</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>135</v>
+      </c>
       <c r="J17" s="19"/>
       <c r="K17" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L17" s="22" t="n">
         <f aca="true">IF(K17="","",TODAY()-K17)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="19" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G18" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H18" s="19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J18" s="19"/>
       <c r="K18" s="21" t="n">
@@ -3488,33 +3680,33 @@
       </c>
       <c r="L18" s="22" t="n">
         <f aca="true">IF(K18="","",TODAY()-K18)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E19" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G19" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
@@ -3523,33 +3715,33 @@
       </c>
       <c r="L19" s="22" t="n">
         <f aca="true">IF(K19="","",TODAY()-K19)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B20" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E20" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G20" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
@@ -3558,105 +3750,105 @@
       </c>
       <c r="L20" s="22" t="n">
         <f aca="true">IF(K20="","",TODAY()-K20)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B21" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G21" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="I21" s="19" t="s">
-        <v>150</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L21" s="22" t="n">
         <f aca="true">IF(K21="","",TODAY()-K21)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B22" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G22" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>149</v>
-      </c>
-      <c r="I22" s="19"/>
+        <v>155</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>156</v>
+      </c>
       <c r="J22" s="19"/>
       <c r="K22" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L22" s="22" t="n">
         <f aca="true">IF(K22="","",TODAY()-K22)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B23" s="20" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G23" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="I23" s="19"/>
       <c r="J23" s="19"/>
@@ -3665,156 +3857,152 @@
       </c>
       <c r="L23" s="22" t="n">
         <f aca="true">IF(K23="","",TODAY()-K23)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G24" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H24" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>161</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="I24" s="19"/>
       <c r="J24" s="19"/>
       <c r="K24" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L24" s="22" t="n">
         <f aca="true">IF(K24="","",TODAY()-K24)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G25" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H25" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="I25" s="19"/>
+        <v>167</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>168</v>
+      </c>
       <c r="J25" s="19"/>
       <c r="K25" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L25" s="22" t="n">
         <f aca="true">IF(K25="","",TODAY()-K25)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>166</v>
-      </c>
       <c r="D26" s="19" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="F26" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G26" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H26" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="I26" s="19" t="s">
-        <v>169</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="I26" s="19"/>
       <c r="J26" s="19"/>
       <c r="K26" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L26" s="22" t="n">
         <f aca="true">IF(K26="","",TODAY()-K26)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G27" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H27" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="I27" s="19" t="s">
         <v>174</v>
       </c>
+      <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L27" s="22" t="n">
         <f aca="true">IF(K27="","",TODAY()-K27)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
         <v>175</v>
       </c>
@@ -3831,7 +4019,7 @@
         <v>76</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G28" s="19" t="s">
         <v>84</v>
@@ -3848,10 +4036,10 @@
       </c>
       <c r="L28" s="22" t="n">
         <f aca="true">IF(K28="","",TODAY()-K28)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
         <v>180</v>
       </c>
@@ -3859,22 +4047,22 @@
         <v>30</v>
       </c>
       <c r="C29" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="D29" s="19" t="s">
         <v>181</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>182</v>
       </c>
       <c r="E29" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G29" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H29" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
@@ -3883,24 +4071,24 @@
       </c>
       <c r="L29" s="22" t="n">
         <f aca="true">IF(K29="","",TODAY()-K29)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="D30" s="19" t="s">
-        <v>186</v>
-      </c>
       <c r="E30" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>11</v>
@@ -3909,16 +4097,18 @@
         <v>84</v>
       </c>
       <c r="H30" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="I30" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="I30" s="19"/>
       <c r="J30" s="19"/>
       <c r="K30" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L30" s="22" t="n">
         <f aca="true">IF(K30="","",TODAY()-K30)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3926,7 +4116,7 @@
         <v>188</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="19" t="s">
         <v>189</v>
@@ -3938,10 +4128,10 @@
         <v>76</v>
       </c>
       <c r="F31" s="19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G31" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H31" s="19" t="s">
         <v>191</v>
@@ -3955,7 +4145,7 @@
       </c>
       <c r="L31" s="22" t="n">
         <f aca="true">IF(K31="","",TODAY()-K31)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3963,13 +4153,13 @@
         <v>193</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="D32" s="19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E32" s="19" t="s">
         <v>76</v>
@@ -3978,13 +4168,13 @@
         <v>11</v>
       </c>
       <c r="G32" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H32" s="19" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I32" s="19" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J32" s="19"/>
       <c r="K32" s="21" t="n">
@@ -3992,21 +4182,21 @@
       </c>
       <c r="L32" s="22" t="n">
         <f aca="true">IF(K32="","",TODAY()-K32)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E33" s="19" t="s">
         <v>76</v>
@@ -4015,21 +4205,19 @@
         <v>11</v>
       </c>
       <c r="G33" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="I33" s="19" t="s">
         <v>201</v>
       </c>
+      <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L33" s="22" t="n">
         <f aca="true">IF(K33="","",TODAY()-K33)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4037,7 +4225,7 @@
         <v>202</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C34" s="19" t="s">
         <v>203</v>
@@ -4046,10 +4234,10 @@
         <v>204</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>84</v>
@@ -4064,7 +4252,7 @@
       </c>
       <c r="L34" s="22" t="n">
         <f aca="true">IF(K34="","",TODAY()-K34)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4072,7 +4260,7 @@
         <v>206</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C35" s="19" t="s">
         <v>207</v>
@@ -4084,10 +4272,10 @@
         <v>76</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H35" s="19" t="s">
         <v>209</v>
@@ -4101,18 +4289,18 @@
       </c>
       <c r="L35" s="22" t="n">
         <f aca="true">IF(K35="","",TODAY()-K35)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
         <v>211</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C36" s="19" t="s">
-        <v>158</v>
+        <v>74</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>212</v>
@@ -4129,28 +4317,30 @@
       <c r="H36" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="I36" s="19"/>
+      <c r="I36" s="19" t="s">
+        <v>214</v>
+      </c>
       <c r="J36" s="19"/>
       <c r="K36" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L36" s="22" t="n">
         <f aca="true">IF(K36="","",TODAY()-K36)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="D37" s="19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E37" s="19" t="s">
         <v>76</v>
@@ -4159,33 +4349,35 @@
         <v>11</v>
       </c>
       <c r="G37" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="I37" s="19"/>
+        <v>218</v>
+      </c>
+      <c r="I37" s="19" t="s">
+        <v>219</v>
+      </c>
       <c r="J37" s="19"/>
       <c r="K37" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L37" s="22" t="n">
         <f aca="true">IF(K37="","",TODAY()-K37)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="D38" s="19" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E38" s="19" t="s">
         <v>76</v>
@@ -4197,7 +4389,7 @@
         <v>84</v>
       </c>
       <c r="H38" s="19" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
@@ -4206,21 +4398,21 @@
       </c>
       <c r="L38" s="22" t="n">
         <f aca="true">IF(K38="","",TODAY()-K38)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>181</v>
+        <v>225</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>76</v>
@@ -4232,10 +4424,10 @@
         <v>102</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="I39" s="19" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="J39" s="19"/>
       <c r="K39" s="21" t="n">
@@ -4243,33 +4435,33 @@
       </c>
       <c r="L39" s="22" t="n">
         <f aca="true">IF(K39="","",TODAY()-K39)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="D40" s="19" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F40" s="19" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="G40" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
@@ -4278,21 +4470,21 @@
       </c>
       <c r="L40" s="22" t="n">
         <f aca="true">IF(K40="","",TODAY()-K40)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E41" s="19" t="s">
         <v>76</v>
@@ -4304,7 +4496,7 @@
         <v>102</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
@@ -4313,105 +4505,105 @@
       </c>
       <c r="L41" s="22" t="n">
         <f aca="true">IF(K41="","",TODAY()-K41)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B42" s="20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>95</v>
+        <v>221</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E42" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G42" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>232</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="I42" s="19"/>
       <c r="J42" s="19"/>
       <c r="K42" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L42" s="22" t="n">
         <f aca="true">IF(K42="","",TODAY()-K42)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="E43" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G43" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="I43" s="19"/>
+        <v>231</v>
+      </c>
+      <c r="I43" s="19" t="s">
+        <v>240</v>
+      </c>
       <c r="J43" s="19"/>
       <c r="K43" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L43" s="22" t="n">
         <f aca="true">IF(K43="","",TODAY()-K43)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E44" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G44" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="I44" s="19"/>
       <c r="J44" s="19"/>
@@ -4420,21 +4612,21 @@
       </c>
       <c r="L44" s="22" t="n">
         <f aca="true">IF(K44="","",TODAY()-K44)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>76</v>
@@ -4443,73 +4635,73 @@
         <v>11</v>
       </c>
       <c r="G45" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="I45" s="19" t="s">
-        <v>244</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="I45" s="19"/>
       <c r="J45" s="19"/>
       <c r="K45" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L45" s="22" t="n">
         <f aca="true">IF(K45="","",TODAY()-K45)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C46" s="19" t="s">
-        <v>241</v>
+        <v>95</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="I46" s="19"/>
+        <v>249</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>250</v>
+      </c>
       <c r="J46" s="19"/>
       <c r="K46" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L46" s="22" t="n">
         <f aca="true">IF(K46="","",TODAY()-K46)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F47" s="19" t="s">
         <v>26</v>
@@ -4518,7 +4710,7 @@
         <v>102</v>
       </c>
       <c r="H47" s="19" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
@@ -4527,142 +4719,140 @@
       </c>
       <c r="L47" s="22" t="n">
         <f aca="true">IF(K47="","",TODAY()-K47)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C48" s="19" t="s">
-        <v>189</v>
+        <v>255</v>
       </c>
       <c r="D48" s="19" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E48" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F48" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G48" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H48" s="19" t="s">
-        <v>253</v>
-      </c>
-      <c r="I48" s="19" t="s">
-        <v>254</v>
-      </c>
+        <v>257</v>
+      </c>
+      <c r="I48" s="19"/>
       <c r="J48" s="19"/>
       <c r="K48" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L48" s="22" t="n">
         <f aca="true">IF(K48="","",TODAY()-K48)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>203</v>
+        <v>259</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F49" s="19" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="G49" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H49" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="I49" s="19"/>
+        <v>261</v>
+      </c>
+      <c r="I49" s="19" t="s">
+        <v>262</v>
+      </c>
       <c r="J49" s="19"/>
       <c r="K49" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L49" s="22" t="n">
         <f aca="true">IF(K49="","",TODAY()-K49)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C50" s="19" t="s">
         <v>259</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>76</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G50" s="19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H50" s="19" t="s">
-        <v>261</v>
-      </c>
-      <c r="I50" s="19" t="s">
-        <v>262</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="I50" s="19"/>
       <c r="J50" s="19"/>
       <c r="K50" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L50" s="22" t="n">
         <f aca="true">IF(K50="","",TODAY()-K50)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="E51" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F51" s="19" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G51" s="19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H51" s="19" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I51" s="19"/>
       <c r="J51" s="19"/>
@@ -4671,68 +4861,70 @@
       </c>
       <c r="L51" s="22" t="n">
         <f aca="true">IF(K51="","",TODAY()-K51)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C52" s="19" t="s">
-        <v>267</v>
+        <v>207</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E52" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G52" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="I52" s="19"/>
+        <v>271</v>
+      </c>
+      <c r="I52" s="19" t="s">
+        <v>272</v>
+      </c>
       <c r="J52" s="19"/>
       <c r="K52" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L52" s="22" t="n">
         <f aca="true">IF(K52="","",TODAY()-K52)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="D53" s="19" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>273</v>
+        <v>83</v>
       </c>
       <c r="F53" s="19" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="G53" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H53" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I53" s="19"/>
       <c r="J53" s="19"/>
@@ -4741,105 +4933,105 @@
       </c>
       <c r="L53" s="22" t="n">
         <f aca="true">IF(K53="","",TODAY()-K53)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="19" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C54" s="19" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D54" s="19" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F54" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G54" s="19" t="s">
         <v>77</v>
       </c>
       <c r="H54" s="19" t="s">
-        <v>278</v>
-      </c>
-      <c r="I54" s="19"/>
+        <v>279</v>
+      </c>
+      <c r="I54" s="19" t="s">
+        <v>280</v>
+      </c>
       <c r="J54" s="19"/>
       <c r="K54" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L54" s="22" t="n">
         <f aca="true">IF(K54="","",TODAY()-K54)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="19" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="D55" s="19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E55" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F55" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G55" s="19" t="s">
         <v>77</v>
       </c>
       <c r="H55" s="19" t="s">
-        <v>281</v>
-      </c>
-      <c r="I55" s="19" t="s">
-        <v>282</v>
-      </c>
+        <v>283</v>
+      </c>
+      <c r="I55" s="19"/>
       <c r="J55" s="19"/>
       <c r="K55" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L55" s="22" t="n">
         <f aca="true">IF(K55="","",TODAY()-K55)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="19" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B56" s="20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D56" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E56" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F56" s="19" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G56" s="19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H56" s="19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="I56" s="19"/>
       <c r="J56" s="19"/>
@@ -4848,24 +5040,24 @@
       </c>
       <c r="L56" s="22" t="n">
         <f aca="true">IF(K56="","",TODAY()-K56)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="19" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B57" s="20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="F57" s="19" t="s">
         <v>11</v>
@@ -4874,7 +5066,7 @@
         <v>102</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I57" s="19"/>
       <c r="J57" s="19"/>
@@ -4883,36 +5075,36 @@
       </c>
       <c r="L57" s="22" t="n">
         <f aca="true">IF(K57="","",TODAY()-K57)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="19" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B58" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C58" s="19" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D58" s="19" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="E58" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F58" s="19" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G58" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H58" s="19" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="I58" s="19" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="J58" s="19"/>
       <c r="K58" s="21" t="n">
@@ -4920,36 +5112,36 @@
       </c>
       <c r="L58" s="22" t="n">
         <f aca="true">IF(K58="","",TODAY()-K58)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="19" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B59" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E59" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G59" s="19" t="s">
         <v>77</v>
       </c>
       <c r="H59" s="19" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="I59" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J59" s="19"/>
       <c r="K59" s="21" t="n">
@@ -4957,58 +5149,56 @@
       </c>
       <c r="L59" s="22" t="n">
         <f aca="true">IF(K59="","",TODAY()-K59)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B60" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C60" s="19" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="I60" s="19" t="s">
-        <v>302</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="I60" s="19"/>
       <c r="J60" s="19"/>
       <c r="K60" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L60" s="22" t="n">
         <f aca="true">IF(K60="","",TODAY()-K60)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="19" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B61" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D61" s="19" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E61" s="19" t="s">
         <v>83</v>
@@ -5017,35 +5207,33 @@
         <v>11</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H61" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="I61" s="19" t="s">
-        <v>307</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="I61" s="19"/>
       <c r="J61" s="19"/>
       <c r="K61" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L61" s="22" t="n">
         <f aca="true">IF(K61="","",TODAY()-K61)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B62" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>166</v>
+        <v>310</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>83</v>
@@ -5057,82 +5245,84 @@
         <v>84</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="I62" s="19"/>
+        <v>312</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>313</v>
+      </c>
       <c r="J62" s="19"/>
       <c r="K62" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L62" s="22" t="n">
         <f aca="true">IF(K62="","",TODAY()-K62)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="19" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B63" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F63" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H63" s="19" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I63" s="19" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="J63" s="19"/>
       <c r="K63" s="21" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="L63" s="22" t="n">
         <f aca="true">IF(K63="","",TODAY()-K63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="B64" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>241</v>
-      </c>
       <c r="D64" s="19" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F64" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H64" s="19" t="s">
         <v>317</v>
       </c>
       <c r="I64" s="19" t="s">
-        <v>244</v>
+        <v>318</v>
       </c>
       <c r="J64" s="19"/>
       <c r="K64" s="21" t="n">
@@ -5140,24 +5330,24 @@
       </c>
       <c r="L64" s="22" t="n">
         <f aca="true">IF(K64="","",TODAY()-K64)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="19" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>95</v>
+        <v>322</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F65" s="19" t="s">
         <v>11</v>
@@ -5166,10 +5356,10 @@
         <v>84</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="I65" s="19" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J65" s="19"/>
       <c r="K65" s="21" t="n">
@@ -5177,21 +5367,21 @@
       </c>
       <c r="L65" s="22" t="n">
         <f aca="true">IF(K65="","",TODAY()-K65)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="19" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B66" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C66" s="19" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D66" s="19" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="E66" s="19" t="s">
         <v>83</v>
@@ -5203,7 +5393,7 @@
         <v>84</v>
       </c>
       <c r="H66" s="19" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="I66" s="19"/>
       <c r="J66" s="19"/>
@@ -5212,58 +5402,58 @@
       </c>
       <c r="L66" s="22" t="n">
         <f aca="true">IF(K66="","",TODAY()-K66)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="19" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B67" s="20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>189</v>
+        <v>310</v>
       </c>
       <c r="D67" s="19" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="E67" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F67" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H67" s="19" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="I67" s="19" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J67" s="19"/>
       <c r="K67" s="21" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="L67" s="22" t="n">
         <f aca="true">IF(K67="","",TODAY()-K67)</f>
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="19" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B68" s="20" t="s">
         <v>55</v>
       </c>
       <c r="C68" s="19" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="D68" s="19" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="E68" s="19" t="s">
         <v>76</v>
@@ -5272,105 +5462,107 @@
         <v>11</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H68" s="19" t="s">
-        <v>331</v>
-      </c>
-      <c r="I68" s="19"/>
+        <v>335</v>
+      </c>
+      <c r="I68" s="19" t="s">
+        <v>262</v>
+      </c>
       <c r="J68" s="19"/>
       <c r="K68" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L68" s="22" t="n">
         <f aca="true">IF(K68="","",TODAY()-K68)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="19" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B69" s="20" t="s">
         <v>55</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>271</v>
+        <v>95</v>
       </c>
       <c r="D69" s="19" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E69" s="19" t="s">
-        <v>273</v>
+        <v>76</v>
       </c>
       <c r="F69" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G69" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H69" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="I69" s="19"/>
+        <v>338</v>
+      </c>
+      <c r="I69" s="19" t="s">
+        <v>339</v>
+      </c>
       <c r="J69" s="19"/>
       <c r="K69" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L69" s="22" t="n">
         <f aca="true">IF(K69="","",TODAY()-K69)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="19" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="B70" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C70" s="19" t="s">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="D70" s="19" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E70" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F70" s="19" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G70" s="19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H70" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="I70" s="19" t="s">
-        <v>339</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="I70" s="19"/>
       <c r="J70" s="19"/>
       <c r="K70" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L70" s="22" t="n">
         <f aca="true">IF(K70="","",TODAY()-K70)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="19" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B71" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="D71" s="19" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E71" s="19" t="s">
         <v>83</v>
@@ -5379,45 +5571,47 @@
         <v>11</v>
       </c>
       <c r="G71" s="19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H71" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="I71" s="19"/>
+        <v>345</v>
+      </c>
+      <c r="I71" s="19" t="s">
+        <v>346</v>
+      </c>
       <c r="J71" s="19"/>
       <c r="K71" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L71" s="22" t="n">
         <f aca="true">IF(K71="","",TODAY()-K71)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="19" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B72" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C72" s="19" t="s">
-        <v>336</v>
+        <v>207</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E72" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F72" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G72" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H72" s="19" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="I72" s="19"/>
       <c r="J72" s="19"/>
@@ -5426,33 +5620,33 @@
       </c>
       <c r="L72" s="22" t="n">
         <f aca="true">IF(K72="","",TODAY()-K72)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="19" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B73" s="20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>336</v>
+        <v>289</v>
       </c>
       <c r="D73" s="19" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E73" s="19" t="s">
-        <v>83</v>
+        <v>291</v>
       </c>
       <c r="F73" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G73" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="I73" s="19"/>
       <c r="J73" s="19"/>
@@ -5461,33 +5655,33 @@
       </c>
       <c r="L73" s="22" t="n">
         <f aca="true">IF(K73="","",TODAY()-K73)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="19" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B74" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C74" s="19" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>83</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G74" s="19" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="I74" s="19"/>
       <c r="J74" s="19"/>
@@ -5496,24 +5690,24 @@
       </c>
       <c r="L74" s="22" t="n">
         <f aca="true">IF(K74="","",TODAY()-K74)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="19" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B75" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D75" s="19" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="E75" s="19" t="s">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="F75" s="19" t="s">
         <v>11</v>
@@ -5522,30 +5716,32 @@
         <v>77</v>
       </c>
       <c r="H75" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="I75" s="19"/>
+        <v>359</v>
+      </c>
+      <c r="I75" s="19" t="s">
+        <v>360</v>
+      </c>
       <c r="J75" s="19"/>
       <c r="K75" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L75" s="22" t="n">
         <f aca="true">IF(K75="","",TODAY()-K75)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="19" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="B76" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="E76" s="19" t="s">
         <v>83</v>
@@ -5557,7 +5753,7 @@
         <v>84</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I76" s="19"/>
       <c r="J76" s="19"/>
@@ -5566,21 +5762,21 @@
       </c>
       <c r="L76" s="22" t="n">
         <f aca="true">IF(K76="","",TODAY()-K76)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="19" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B77" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>83</v>
@@ -5592,10 +5788,10 @@
         <v>84</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="I77" s="19" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="J77" s="19"/>
       <c r="K77" s="21" t="n">
@@ -5603,73 +5799,71 @@
       </c>
       <c r="L77" s="22" t="n">
         <f aca="true">IF(K77="","",TODAY()-K77)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="19" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B78" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C78" s="19" t="s">
-        <v>74</v>
+        <v>354</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F78" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G78" s="19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="I78" s="19" t="s">
-        <v>363</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="I78" s="19"/>
       <c r="J78" s="19"/>
       <c r="K78" s="21" t="n">
         <v>46292</v>
       </c>
       <c r="L78" s="22" t="n">
         <f aca="true">IF(K78="","",TODAY()-K78)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="19" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B79" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>140</v>
+        <v>369</v>
       </c>
       <c r="D79" s="19" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E79" s="19" t="s">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="F79" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G79" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H79" s="19" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="I79" s="19" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J79" s="19"/>
       <c r="K79" s="21" t="n">
@@ -5677,36 +5871,36 @@
       </c>
       <c r="L79" s="22" t="n">
         <f aca="true">IF(K79="","",TODAY()-K79)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="19" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="B80" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>189</v>
+        <v>369</v>
       </c>
       <c r="D80" s="19" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="E80" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="G80" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H80" s="19" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I80" s="19" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="J80" s="19"/>
       <c r="K80" s="21" t="n">
@@ -5714,36 +5908,36 @@
       </c>
       <c r="L80" s="22" t="n">
         <f aca="true">IF(K80="","",TODAY()-K80)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="19" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B81" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>336</v>
+        <v>369</v>
       </c>
       <c r="D81" s="19" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="E81" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F81" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G81" s="19" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="H81" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I81" s="19" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J81" s="19"/>
       <c r="K81" s="21" t="n">
@@ -5751,12 +5945,12 @@
       </c>
       <c r="L81" s="22" t="n">
         <f aca="true">IF(K81="","",TODAY()-K81)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="19" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B82" s="20" t="s">
         <v>57</v>
@@ -5765,7 +5959,7 @@
         <v>74</v>
       </c>
       <c r="D82" s="19" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E82" s="19" t="s">
         <v>76</v>
@@ -5774,13 +5968,13 @@
         <v>11</v>
       </c>
       <c r="G82" s="19" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="H82" s="19" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="I82" s="19" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="J82" s="19"/>
       <c r="K82" s="21" t="n">
@@ -5788,24 +5982,24 @@
       </c>
       <c r="L82" s="22" t="n">
         <f aca="true">IF(K82="","",TODAY()-K82)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="19" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="B83" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="D83" s="19" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F83" s="19" t="s">
         <v>11</v>
@@ -5814,10 +6008,10 @@
         <v>84</v>
       </c>
       <c r="H83" s="19" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="I83" s="19" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="J83" s="19"/>
       <c r="K83" s="21" t="n">
@@ -5825,36 +6019,36 @@
       </c>
       <c r="L83" s="22" t="n">
         <f aca="true">IF(K83="","",TODAY()-K83)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="19" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="B84" s="20" t="s">
         <v>57</v>
       </c>
       <c r="C84" s="19" t="s">
-        <v>241</v>
+        <v>207</v>
       </c>
       <c r="D84" s="19" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>352</v>
+        <v>76</v>
       </c>
       <c r="F84" s="19" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G84" s="19" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H84" s="19" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I84" s="19" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="J84" s="19"/>
       <c r="K84" s="21" t="n">
@@ -5862,95 +6056,95 @@
       </c>
       <c r="L84" s="22" t="n">
         <f aca="true">IF(K84="","",TODAY()-K84)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="19" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B85" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>74</v>
+        <v>354</v>
       </c>
       <c r="D85" s="19" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E85" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F85" s="19" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G85" s="19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H85" s="19" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="I85" s="19" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J85" s="19"/>
       <c r="K85" s="21" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="L85" s="22" t="n">
         <f aca="true">IF(K85="","",TODAY()-K85)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="19" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="B86" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C86" s="19" t="s">
-        <v>393</v>
+        <v>74</v>
       </c>
       <c r="D86" s="19" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E86" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F86" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G86" s="19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H86" s="19" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="I86" s="19" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="J86" s="19"/>
       <c r="K86" s="21" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="L86" s="22" t="n">
         <f aca="true">IF(K86="","",TODAY()-K86)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="19" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B87" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>393</v>
+        <v>95</v>
       </c>
       <c r="D87" s="19" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E87" s="19" t="s">
         <v>83</v>
@@ -5959,38 +6153,38 @@
         <v>11</v>
       </c>
       <c r="G87" s="19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H87" s="19" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="I87" s="19" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="J87" s="19"/>
       <c r="K87" s="21" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="L87" s="22" t="n">
         <f aca="true">IF(K87="","",TODAY()-K87)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="19" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B88" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>402</v>
+        <v>259</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E88" s="19" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="F88" s="19" t="s">
         <v>11</v>
@@ -5999,35 +6193,35 @@
         <v>84</v>
       </c>
       <c r="H88" s="19" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="I88" s="19" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J88" s="19"/>
       <c r="K88" s="21" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="L88" s="22" t="n">
         <f aca="true">IF(K88="","",TODAY()-K88)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="19" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B89" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>393</v>
+        <v>207</v>
       </c>
       <c r="D89" s="19" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E89" s="19" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F89" s="19" t="s">
         <v>11</v>
@@ -6036,35 +6230,35 @@
         <v>84</v>
       </c>
       <c r="H89" s="19" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="I89" s="19" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="J89" s="19"/>
       <c r="K89" s="21" t="n">
-        <v>46293</v>
+        <v>46292</v>
       </c>
       <c r="L89" s="22" t="n">
         <f aca="true">IF(K89="","",TODAY()-K89)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="19" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B90" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C90" s="19" t="s">
-        <v>291</v>
+        <v>74</v>
       </c>
       <c r="D90" s="19" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E90" s="19" t="s">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="F90" s="19" t="s">
         <v>20</v>
@@ -6073,10 +6267,10 @@
         <v>77</v>
       </c>
       <c r="H90" s="19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="I90" s="19" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J90" s="19"/>
       <c r="K90" s="21" t="n">
@@ -6084,36 +6278,36 @@
       </c>
       <c r="L90" s="22" t="n">
         <f aca="true">IF(K90="","",TODAY()-K90)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="19" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B91" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>291</v>
+        <v>417</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E91" s="19" t="s">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G91" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="I91" s="19" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J91" s="19"/>
       <c r="K91" s="21" t="n">
@@ -6121,36 +6315,36 @@
       </c>
       <c r="L91" s="22" t="n">
         <f aca="true">IF(K91="","",TODAY()-K91)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="19" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="B92" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C92" s="19" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D92" s="19" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E92" s="19" t="s">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="F92" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G92" s="19" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H92" s="19" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I92" s="19" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J92" s="19"/>
       <c r="K92" s="21" t="n">
@@ -6158,36 +6352,36 @@
       </c>
       <c r="L92" s="22" t="n">
         <f aca="true">IF(K92="","",TODAY()-K92)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="19" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B93" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>74</v>
+        <v>426</v>
       </c>
       <c r="D93" s="19" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E93" s="19" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="F93" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G93" s="19" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="H93" s="19" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="I93" s="19" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J93" s="19"/>
       <c r="K93" s="21" t="n">
@@ -6195,36 +6389,36 @@
       </c>
       <c r="L93" s="22" t="n">
         <f aca="true">IF(K93="","",TODAY()-K93)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="19" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B94" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C94" s="19" t="s">
-        <v>74</v>
+        <v>417</v>
       </c>
       <c r="D94" s="19" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E94" s="19" t="s">
-        <v>352</v>
+        <v>83</v>
       </c>
       <c r="F94" s="19" t="s">
         <v>11</v>
       </c>
       <c r="G94" s="19" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H94" s="19" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="I94" s="19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J94" s="19"/>
       <c r="K94" s="21" t="n">
@@ -6232,15 +6426,523 @@
       </c>
       <c r="L94" s="22" t="n">
         <f aca="true">IF(K94="","",TODAY()-K94)</f>
-        <v>0</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="19" t="s">
+        <v>434</v>
+      </c>
+      <c r="B95" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C95" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D95" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="E95" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F95" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G95" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H95" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="I95" s="19" t="s">
+        <v>437</v>
+      </c>
+      <c r="J95" s="19"/>
+      <c r="K95" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <f aca="true">IF(K95="","",TODAY()-K95)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="B96" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D96" s="19" t="s">
+        <v>439</v>
+      </c>
+      <c r="E96" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G96" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H96" s="19" t="s">
+        <v>440</v>
+      </c>
+      <c r="I96" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="J96" s="19"/>
+      <c r="K96" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <f aca="true">IF(K96="","",TODAY()-K96)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="19" t="s">
+        <v>442</v>
+      </c>
+      <c r="B97" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C97" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="D97" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="E97" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F97" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H97" s="19" t="s">
+        <v>445</v>
+      </c>
+      <c r="I97" s="19" t="s">
+        <v>446</v>
+      </c>
+      <c r="J97" s="19"/>
+      <c r="K97" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <f aca="true">IF(K97="","",TODAY()-K97)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C98" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D98" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="E98" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F98" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G98" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="I98" s="19" t="s">
+        <v>450</v>
+      </c>
+      <c r="J98" s="19"/>
+      <c r="K98" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <f aca="true">IF(K98="","",TODAY()-K98)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="B99" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C99" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D99" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="E99" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="F99" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G99" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" s="19" t="s">
+        <v>453</v>
+      </c>
+      <c r="I99" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="J99" s="19"/>
+      <c r="K99" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <f aca="true">IF(K99="","",TODAY()-K99)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="B100" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C100" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D100" s="19" t="s">
+        <v>456</v>
+      </c>
+      <c r="E100" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F100" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G100" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H100" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="I100" s="19" t="s">
+        <v>458</v>
+      </c>
+      <c r="J100" s="19"/>
+      <c r="K100" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L100" s="22" t="n">
+        <f aca="true">IF(K100="","",TODAY()-K100)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="B101" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C101" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D101" s="19" t="s">
+        <v>460</v>
+      </c>
+      <c r="E101" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F101" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H101" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="I101" s="19"/>
+      <c r="J101" s="19"/>
+      <c r="K101" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L101" s="22" t="n">
+        <f aca="true">IF(K101="","",TODAY()-K101)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="19" t="s">
+        <v>462</v>
+      </c>
+      <c r="B102" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C102" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D102" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F102" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H102" s="19" t="s">
+        <v>464</v>
+      </c>
+      <c r="I102" s="19"/>
+      <c r="J102" s="19"/>
+      <c r="K102" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L102" s="22" t="n">
+        <f aca="true">IF(K102="","",TODAY()-K102)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="B103" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D103" s="19" t="s">
+        <v>466</v>
+      </c>
+      <c r="E103" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F103" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G103" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H103" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="I103" s="19"/>
+      <c r="J103" s="19"/>
+      <c r="K103" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L103" s="22" t="n">
+        <f aca="true">IF(K103="","",TODAY()-K103)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="19" t="s">
+        <v>468</v>
+      </c>
+      <c r="B104" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C104" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D104" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="E104" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F104" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H104" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="I104" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="J104" s="19"/>
+      <c r="K104" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L104" s="22" t="n">
+        <f aca="true">IF(K104="","",TODAY()-K104)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="19" t="s">
+        <v>472</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D105" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F105" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G105" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H105" s="19" t="s">
+        <v>474</v>
+      </c>
+      <c r="I105" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="J105" s="19"/>
+      <c r="K105" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L105" s="22" t="n">
+        <f aca="true">IF(K105="","",TODAY()-K105)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="B106" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D106" s="19" t="s">
+        <v>476</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F106" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G106" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H106" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="I106" s="19"/>
+      <c r="J106" s="19"/>
+      <c r="K106" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <f aca="true">IF(K106="","",TODAY()-K106)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="19" t="s">
+        <v>478</v>
+      </c>
+      <c r="B107" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D107" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F107" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G107" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H107" s="19" t="s">
+        <v>480</v>
+      </c>
+      <c r="I107" s="19"/>
+      <c r="J107" s="19"/>
+      <c r="K107" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <f aca="true">IF(K107="","",TODAY()-K107)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="B108" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D108" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="E108" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="F108" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G108" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="H108" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="I108" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="J108" s="19"/>
+      <c r="K108" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="L108" s="22" t="n">
+        <f aca="true">IF(K108="","",TODAY()-K108)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L94"/>
+  <autoFilter ref="A4:L108"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:L294">
+  <conditionalFormatting sqref="A5:L308">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$F5="No iniciado"</formula>
     </cfRule>
@@ -6263,29 +6965,29 @@
       <formula>$F5="Por verificar"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G294">
+  <conditionalFormatting sqref="G5:G308">
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>AND($G5="Alta",$F5&lt;&gt;"Terminado",$F5&lt;&gt;"Descartado")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
-    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F5:F294" type="list">
+    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="F5:F308" type="list">
       <formula1>"No iniciado,En progreso,Parcial,Terminado,Bloqueado,Descartado,Por verificar"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5:G294" type="list">
+    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="G5:G308" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E294" type="list">
+    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E308" type="list">
       <formula1>"Pendiente del plan,Observación / defecto,Trabajo futuro,Decisión pendiente,Mantenimiento de docs"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J294" type="list">
+    <dataValidation allowBlank="true" error="Elija un valor de la lista." errorStyle="stop" errorTitle="Valor no válido" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J5:J308" type="list">
       <formula1>"Luis,Elizabeth,Miguel,Equipo,Agente (Claude Code)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Escriba una fecha (dd-mm-aaaa)." errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K294" type="date">
+    <dataValidation allowBlank="true" error="Escriba una fecha (dd-mm-aaaa)." errorStyle="stop" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K308" type="date">
       <formula1>DATE(2026,1,1)</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6307,7 +7009,7 @@
     <tabColor rgb="FF3A3F6E"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
@@ -6319,32 +7021,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>431</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>432</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="B4" s="23" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>434</v>
+        <v>488</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>436</v>
+        <v>490</v>
       </c>
       <c r="F4" s="23" t="s">
-        <v>437</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6352,19 +7054,19 @@
         <v>46292</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>439</v>
+        <v>493</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>440</v>
+        <v>494</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6372,19 +7074,19 @@
         <v>46293</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>441</v>
+        <v>495</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>438</v>
+        <v>492</v>
       </c>
       <c r="D6" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>439</v>
+        <v>493</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>442</v>
+        <v>496</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6392,7 +7094,7 @@
         <v>46293</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>443</v>
+        <v>497</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>11</v>
@@ -6401,10 +7103,10 @@
         <v>20</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>444</v>
+        <v>498</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>445</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6412,7 +7114,7 @@
         <v>46293</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>446</v>
+        <v>500</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>11</v>
@@ -6421,23 +7123,83 @@
         <v>29</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>439</v>
+        <v>493</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>447</v>
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>502</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>503</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>505</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>506</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>508</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>509</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C9:C500" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C12:C500" type="list">
       <formula1>"No iniciado,En progreso,Parcial,Terminado,Bloqueado,Descartado,Por verificar"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D9:D500" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D12:D500" type="list">
       <formula1>"No iniciado,En progreso,Parcial,Terminado,Bloqueado,Descartado,Por verificar"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E9:E500" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E12:E500" type="list">
       <formula1>"Luis,Elizabeth,Miguel,Equipo,Agente (Claude Code)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6468,7 +7230,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>448</v>
+        <v>510</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6479,7 +7241,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>449</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6488,7 +7250,7 @@
         <v>14</v>
       </c>
       <c r="C4" s="25" t="s">
-        <v>450</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6497,7 +7259,7 @@
         <v>17</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>451</v>
+        <v>513</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6506,7 +7268,7 @@
         <v>20</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>452</v>
+        <v>514</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6515,7 +7277,7 @@
         <v>23</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>453</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6524,7 +7286,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>454</v>
+        <v>516</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6533,7 +7295,7 @@
         <v>29</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>455</v>
+        <v>517</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6544,7 +7306,7 @@
         <v>83</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>456</v>
+        <v>518</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6553,7 +7315,7 @@
         <v>76</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>457</v>
+        <v>519</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6562,25 +7324,25 @@
         <v>101</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>458</v>
+        <v>520</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14"/>
       <c r="B13" s="25" t="s">
-        <v>352</v>
+        <v>133</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>459</v>
+        <v>521</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="14"/>
       <c r="B14" s="25" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>460</v>
+        <v>522</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6588,10 +7350,10 @@
         <v>63</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>461</v>
+        <v>523</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6599,10 +7361,10 @@
         <v>72</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>462</v>
+        <v>524</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>463</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$117</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -892,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="32" min="1" max="1"/>
@@ -1647,6 +1647,34 @@
       </c>
       <c r="J24" s="38">
         <f>COUNTIF(Pendientes!$B$5:$B$308,E24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="33">
+      <c r="E25" s="40" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F25" s="38" t="inlineStr">
+        <is>
+          <t>IA con valor, medida y con privacidad</t>
+        </is>
+      </c>
+      <c r="G25" s="38">
+        <f>COUNTIFS(Pendientes!$B$5:$B$308,E25,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E25,Pendientes!$F$5:$F$308,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="38">
+        <f>COUNTIFS(Pendientes!$B$5:$B$308,E25,Pendientes!$F$5:$F$308,"Terminado")</f>
+        <v/>
+      </c>
+      <c r="I25" s="38">
+        <f>COUNTIFS(Pendientes!$B$5:$B$308,E25,Pendientes!$F$5:$F$308,"Descartado")</f>
+        <v/>
+      </c>
+      <c r="J25" s="38">
+        <f>COUNTIF(Pendientes!$B$5:$B$308,E25)</f>
         <v/>
       </c>
     </row>
@@ -1669,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="32" min="1" max="1"/>
@@ -3615,12 +3643,12 @@
       </c>
       <c r="I39" s="51" t="inlineStr">
         <is>
-          <t>Se resuelve con datos reales del piloto; no requiere código.</t>
+          <t>Ya no se resuelve con los datos del piloto: el modo básico no muestra la IA y el piloto no la evalúa (plan 23). Con el evaluador corregido (P23-01) se podrá medir en el modo avanzado.</t>
         </is>
       </c>
       <c r="J39" s="51" t="n"/>
       <c r="K39" s="53" t="n">
-        <v>46292</v>
+        <v>46301</v>
       </c>
       <c r="L39" s="54">
         <f>IF(K39="","",TODAY()-K39)</f>
@@ -4860,7 +4888,7 @@
       </c>
       <c r="F63" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>En progreso</t>
         </is>
       </c>
       <c r="G63" s="51" t="inlineStr">
@@ -4870,12 +4898,12 @@
       </c>
       <c r="H63" s="51" t="inlineStr">
         <is>
-          <t>Plan 19, sección 3.4.</t>
+          <t>Plan 19, sección 3.4; rama feat/modo-basico-web (subida al remoto, commits ce91ec7, e2e238a, 6aa9be3).</t>
         </is>
       </c>
       <c r="I63" s="51" t="inlineStr">
         <is>
-          <t>ANTES DE LA VISITA (decisión del 6-oct): el piloto va con la web. /pedir (fase C) solo para el Administrador; sin cambios de permisos.</t>
+          <t>Fases A, B y C implementadas y verificadas (pruebas, mutaciones y navegador). Falta: mezclar a main (la migración de modo_interfaz corre sola al desplegar), probar en celular y con un Administrador con 2FA.</t>
         </is>
       </c>
       <c r="J63" s="51" t="n"/>
@@ -7314,8 +7342,523 @@
         <v/>
       </c>
     </row>
+    <row r="109" ht="23.85" customHeight="1" s="33">
+      <c r="A109" s="51" t="inlineStr">
+        <is>
+          <t>P23-01</t>
+        </is>
+      </c>
+      <c r="B109" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C109" s="51" t="inlineStr">
+        <is>
+          <t>Evaluador</t>
+        </is>
+      </c>
+      <c r="D109" s="51" t="inlineStr">
+        <is>
+          <t>El evaluador de Feedback_IA compara un número equivocado: sugerencia_ia guarda el % de ajuste de la IA y feedbackController.js:99 lo usa como cantidad. Corregirlo y decidir qué cantidad(es) se evalúan (propuesta: motor, IA ajustada y lo que pidió el dueño)</t>
+        </is>
+      </c>
+      <c r="E109" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F109" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G109" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H109" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, secciones 1 y 3.A. controllers/feedbackController.js:99; ordenBorradorController.js:102.</t>
+        </is>
+      </c>
+      <c r="I109" s="51" t="inlineStr">
+        <is>
+          <t>Antes del arranque del piloto. Decisión 1 de Luis. Probablemente requiere migración (columnas nuevas en Feedback_IA). Cambia el factor que usan alertas y Proveedores.</t>
+        </is>
+      </c>
+      <c r="J109" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K109" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L109" s="54">
+        <f>IF(K109="","",TODAY()-K109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="23.85" customHeight="1" s="33">
+      <c r="A110" s="51" t="inlineStr">
+        <is>
+          <t>P23-02</t>
+        </is>
+      </c>
+      <c r="B110" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C110" s="51" t="inlineStr">
+        <is>
+          <t>Medición</t>
+        </is>
+      </c>
+      <c r="D110" s="51" t="inlineStr">
+        <is>
+          <t>Reporte comparativo: error del motor, de la IA y del dueño frente a las ventas reales, por tienda y producto</t>
+        </is>
+      </c>
+      <c r="E110" s="51" t="inlineStr">
+        <is>
+          <t>Pendiente del plan</t>
+        </is>
+      </c>
+      <c r="F110" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G110" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H110" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, sección 3.A3.</t>
+        </is>
+      </c>
+      <c r="I110" s="51" t="inlineStr">
+        <is>
+          <t>En rama durante el piloto. Depende de P23-01. Sirve también para el documento académico.</t>
+        </is>
+      </c>
+      <c r="J110" s="51" t="n"/>
+      <c r="K110" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L110" s="54">
+        <f>IF(K110="","",TODAY()-K110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="23.85" customHeight="1" s="33">
+      <c r="A111" s="51" t="inlineStr">
+        <is>
+          <t>P23-03</t>
+        </is>
+      </c>
+      <c r="B111" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C111" s="51" t="inlineStr">
+        <is>
+          <t>Motor adaptativo</t>
+        </is>
+      </c>
+      <c r="D111" s="51" t="inlineStr">
+        <is>
+          <t>Estadística sin IA: tiempo real de entrega por proveedor, variabilidad de la demanda, efecto del día de la semana o la quincena</t>
+        </is>
+      </c>
+      <c r="E111" s="51" t="inlineStr">
+        <is>
+          <t>Pendiente del plan</t>
+        </is>
+      </c>
+      <c r="F111" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G111" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H111" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, sección 3.A4.</t>
+        </is>
+      </c>
+      <c r="I111" s="51" t="inlineStr">
+        <is>
+          <t>Opcional. En rama durante el piloto. Es lo más honesto para decir que el motor «se adapta».</t>
+        </is>
+      </c>
+      <c r="J111" s="51" t="n"/>
+      <c r="K111" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L111" s="54">
+        <f>IF(K111="","",TODAY()-K111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="23.85" customHeight="1" s="33">
+      <c r="A112" s="51" t="inlineStr">
+        <is>
+          <t>P23-04</t>
+        </is>
+      </c>
+      <c r="B112" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C112" s="51" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="D112" s="51" t="inlineStr">
+        <is>
+          <t>Darle contexto real al ajuste de la IA (calendario, quincena, festivos, vencimientos) y registrar el contexto en Auditoria_IA</t>
+        </is>
+      </c>
+      <c r="E112" s="51" t="inlineStr">
+        <is>
+          <t>Pendiente del plan</t>
+        </is>
+      </c>
+      <c r="F112" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G112" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H112" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, sección 3.B.</t>
+        </is>
+      </c>
+      <c r="I112" s="51" t="inlineStr">
+        <is>
+          <t>Depende de P23-01 y P23-02: sin medición no se sabe si mejora algo.</t>
+        </is>
+      </c>
+      <c r="J112" s="51" t="n"/>
+      <c r="K112" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L112" s="54">
+        <f>IF(K112="","",TODAY()-K112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="23.85" customHeight="1" s="33">
+      <c r="A113" s="51" t="inlineStr">
+        <is>
+          <t>P23-05</t>
+        </is>
+      </c>
+      <c r="B113" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C113" s="51" t="inlineStr">
+        <is>
+          <t>IA</t>
+        </is>
+      </c>
+      <c r="D113" s="51" t="inlineStr">
+        <is>
+          <t>Leer fotos de facturas del proveedor para dar entrada a mercancía o alta de catálogo, mandando a la IA solo las líneas y sin guardar la imagen</t>
+        </is>
+      </c>
+      <c r="E113" s="51" t="inlineStr">
+        <is>
+          <t>Pendiente del plan</t>
+        </is>
+      </c>
+      <c r="F113" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G113" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H113" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, sección 3.C.</t>
+        </is>
+      </c>
+      <c r="I113" s="51" t="inlineStr">
+        <is>
+          <t>Es el frente más grande. Depende de P23-06 y P23-07 (privacidad). Nunca fotos del cuaderno de fiados.</t>
+        </is>
+      </c>
+      <c r="J113" s="51" t="n"/>
+      <c r="K113" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L113" s="54">
+        <f>IF(K113="","",TODAY()-K113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="23.85" customHeight="1" s="33">
+      <c r="A114" s="51" t="inlineStr">
+        <is>
+          <t>P23-06</t>
+        </is>
+      </c>
+      <c r="B114" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C114" s="51" t="inlineStr">
+        <is>
+          <t>Privacidad</t>
+        </is>
+      </c>
+      <c r="D114" s="51" t="inlineStr">
+        <is>
+          <t>El Consejero manda el nombre del proveedor y las promociones mandan el «motivo del dueño» (texto libre) a OpenAI; la política publicada dice que no se envían datos personales</t>
+        </is>
+      </c>
+      <c r="E114" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F114" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G114" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H114" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, sección 4. controllers/aiController.js (Consejero y getPromotionSuggestions).</t>
+        </is>
+      </c>
+      <c r="I114" s="51" t="inlineStr">
+        <is>
+          <t>Antes del arranque del piloto. Mandar id o etiqueta genérica; ampliar tests/integration/ia_privacidad.test.js. Decisión 3 de Luis.</t>
+        </is>
+      </c>
+      <c r="J114" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K114" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L114" s="54">
+        <f>IF(K114="","",TODAY()-K114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="23.85" customHeight="1" s="33">
+      <c r="A115" s="51" t="inlineStr">
+        <is>
+          <t>P23-07</t>
+        </is>
+      </c>
+      <c r="B115" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C115" s="51" t="inlineStr">
+        <is>
+          <t>Privacidad</t>
+        </is>
+      </c>
+      <c r="D115" s="51" t="inlineStr">
+        <is>
+          <t>Revisión jurídica de lo que se envía a OpenAI (responsable/encargado, transmisión internacional, registro ante la SIC, términos de OpenAI) y reescritura de la política de datos</t>
+        </is>
+      </c>
+      <c r="E115" s="51" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F115" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G115" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H115" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, sección 4 (preguntas). frontend/src/pages/PoliticaDatosPage.jsx.</t>
+        </is>
+      </c>
+      <c r="I115" s="51" t="inlineStr">
+        <is>
+          <t>Antes de activar cualquier función de IA que envíe datos personales o fotos. El equipo no es asesor jurídico: consultar al docente o al consultorio jurídico.</t>
+        </is>
+      </c>
+      <c r="J115" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K115" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L115" s="54">
+        <f>IF(K115="","",TODAY()-K115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="23.85" customHeight="1" s="33">
+      <c r="A116" s="51" t="inlineStr">
+        <is>
+          <t>P23-08</t>
+        </is>
+      </c>
+      <c r="B116" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C116" s="51" t="inlineStr">
+        <is>
+          <t>Documentos</t>
+        </is>
+      </c>
+      <c r="D116" s="51" t="inlineStr">
+        <is>
+          <t>Reposicionar la propuesta de valor: de «usando IA» a motor propio, explicable y auditable con la IA como capa opcional en evaluación; revisar título, objetivo general y objetivo específico 3; no reutilizar cifras sin respaldo (85 %, 28 %, 22 %, 4 h)</t>
+        </is>
+      </c>
+      <c r="E116" s="51" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F116" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G116" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H116" s="51" t="inlineStr">
+        <is>
+          <t>Plan 23, sección 6.</t>
+        </is>
+      </c>
+      <c r="I116" s="51" t="inlineStr">
+        <is>
+          <t>Consultar al docente antes de cambiar título y objetivos. Verificar las citas contra los .docx originales.</t>
+        </is>
+      </c>
+      <c r="J116" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K116" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L116" s="54">
+        <f>IF(K116="","",TODAY()-K116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="23.85" customHeight="1" s="33">
+      <c r="A117" s="51" t="inlineStr">
+        <is>
+          <t>P23-09</t>
+        </is>
+      </c>
+      <c r="B117" s="52" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C117" s="51" t="inlineStr">
+        <is>
+          <t>Privacidad</t>
+        </is>
+      </c>
+      <c r="D117" s="51" t="inlineStr">
+        <is>
+          <t>El análisis de riesgo de un cliente (Cartera) mandaba el nombre del cliente a OpenAI; ahora manda el id</t>
+        </is>
+      </c>
+      <c r="E117" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F117" s="51" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="G117" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H117" s="51" t="inlineStr">
+        <is>
+          <t>Commit afddd1d (rama feat/modo-basico-web); tests/integration/ia_privacidad.test.js (confirmado en rojo antes del arreglo; 4 mutaciones detectadas).</t>
+        </is>
+      </c>
+      <c r="I117" s="51" t="inlineStr">
+        <is>
+          <t>Subido a la rama; falta mezclar a main.</t>
+        </is>
+      </c>
+      <c r="J117" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K117" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="L117" s="54">
+        <f>IF(K117="","",TODAY()-K117)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L108"/>
+  <autoFilter ref="A4:L117"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -7382,7 +7925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -7652,29 +8195,59 @@
       <c r="A12" s="53" t="n">
         <v>46301</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="32" t="inlineStr">
         <is>
           <t>P07-01, P07-02, P07-03, P19-06, P19-07, P21-04, P21-09, P21-13, P21-14, P22-04, P22-05</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="32" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="32" t="inlineStr">
         <is>
           <t>Cambio de rumbo (6-oct): el piloto y la visita van con la web en modo básico (plan 19, 3.4, fases A, B y C; /pedir solo Administrador); la app nativa sigue en paralelo y se presenta en la sustentación (nov.). Panel (I1, I2, I4) antes del piloto, con encuesta de satisfacción. Revierte la decisión del 3-oct. Además, P07-02, P21-09, P21-13 y P21-14 pasan a Terminado: ya están en main (merge cb028d9, verificado con git log).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" s="33">
+      <c r="A13" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P19-06, P11-02, P23-01 a P23-09</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Decisiones del 6-oct: la IA va disponible pero opcional (oculta en el modo básico); se invertirá en corregir el evaluador y medir, contexto real al ajuste y lectura de facturas (plan 23); privacidad primero. Modo básico A, B y C implementado en la rama feat/modo-basico-web (subida). Arreglo de privacidad de Cartera (afddd1d) terminado. Rama del backend y 4 ramas de la app subidas; main sin tocar.</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -7767,7 +7767,7 @@
       </c>
       <c r="F116" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>En progreso</t>
         </is>
       </c>
       <c r="G116" s="51" t="inlineStr">
@@ -7777,12 +7777,12 @@
       </c>
       <c r="H116" s="51" t="inlineStr">
         <is>
-          <t>Plan 23, sección 6.</t>
+          <t>Plan 23, sección 6. Borrador de los textos de reemplazo: Documentacion/StockPilot_Secciones_corregidas_sobre_la_IA.docx (mismo formato que «Plan de Negocio — Secciones corregidas v2»).</t>
         </is>
       </c>
       <c r="I116" s="51" t="inlineStr">
         <is>
-          <t>Consultar al docente antes de cambiar título y objetivos. Verificar las citas contra los .docx originales.</t>
+          <t>Falta que Luis aplique los reemplazos en los documentos originales y consulte al docente antes de cambiar título y objetivos. Verificar los pasajes en Word (se ubicaron en textos extraídos). Seis verificaciones pendientes en la última página del borrador.</t>
         </is>
       </c>
       <c r="J116" s="51" t="inlineStr">
@@ -7925,7 +7925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -8225,29 +8225,59 @@
       <c r="A13" s="53" t="n">
         <v>46301</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="32" t="inlineStr">
         <is>
           <t>P19-06, P11-02, P23-01 a P23-09</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="32" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="32" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="32" t="inlineStr">
         <is>
           <t>Decisiones del 6-oct: la IA va disponible pero opcional (oculta en el modo básico); se invertirá en corregir el evaluador y medir, contexto real al ajuste y lectura de facturas (plan 23); privacidad primero. Modo básico A, B y C implementado en la rama feat/modo-basico-web (subida). Arreglo de privacidad de Cartera (afddd1d) terminado. Rama del backend y 4 ramas de la app subidas; main sin tocar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" s="33">
+      <c r="A14" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P23-08</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>En progreso</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Borrador de las secciones corregidas sobre el alcance de la IA, con el formato del documento «Secciones corregidas v2»: Documentacion/StockPilot_Secciones_corregidas_sobre_la_IA.docx (21 recuadros de instrucción, 4 tablas). Pendiente de que Luis lo aplique.</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -7777,12 +7777,12 @@
       </c>
       <c r="H116" s="51" t="inlineStr">
         <is>
-          <t>Plan 23, sección 6. Borrador de los textos de reemplazo: Documentacion/StockPilot_Secciones_corregidas_sobre_la_IA.docx (mismo formato que «Plan de Negocio — Secciones corregidas v2»).</t>
+          <t>Plan 23, sección 6. Documento único para actualizar el Documento 5 del Drive: Documentacion/Revision_Documento_Practica_5_v2.docx (secciones A a G de la revisión del 26-sep, actualizadas, más H a K nuevas). Reemplaza al borrador «Secciones corregidas sobre la IA».</t>
         </is>
       </c>
       <c r="I116" s="51" t="inlineStr">
         <is>
-          <t>Falta que Luis aplique los reemplazos en los documentos originales y consulte al docente antes de cambiar título y objetivos. Verificar los pasajes en Word (se ubicaron en textos extraídos). Seis verificaciones pendientes en la última página del borrador.</t>
+          <t>Falta que Luis aplique los textos en el Documento 5 y en el Plan de Negocio e Intervención, y que consulte al docente antes de cambiar título y objetivos. Verificar los pasajes en Word/Drive. Nueve verificaciones pendientes en la sección K de la revisión v2.</t>
         </is>
       </c>
       <c r="J116" s="51" t="inlineStr">
@@ -7925,7 +7925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -8255,29 +8255,59 @@
       <c r="A14" s="53" t="n">
         <v>46301</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="32" t="inlineStr">
         <is>
           <t>P23-08</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>No iniciado</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="32" t="inlineStr">
         <is>
           <t>En progreso</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t>Agente (Claude Code)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="32" t="inlineStr">
         <is>
           <t>Borrador de las secciones corregidas sobre el alcance de la IA, con el formato del documento «Secciones corregidas v2»: Documentacion/StockPilot_Secciones_corregidas_sobre_la_IA.docx (21 recuadros de instrucción, 4 tablas). Pendiente de que Luis lo aplique.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" s="33">
+      <c r="A15" s="53" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P23-08</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>En progreso</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>En progreso</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Se consolidó todo en Documentacion/Revision_Documento_Practica_5_v2.docx (24 páginas en Word, 10 tablas): revisión del 26-sep actualizada al 6-oct (pruebas 287 + 407, 28,2 KLOC, escáner, rol «Colaborador»), reglas de alertas, textos de la IA, novedades y correcciones a Plan de Negocio, Intervención y Herramientas. Se retira el borrador anterior «Secciones corregidas sobre la IA».</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -1697,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L117"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="32" min="1" max="1"/>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="F75" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Por verificar</t>
         </is>
       </c>
       <c r="G75" s="51" t="inlineStr">
@@ -5538,17 +5538,21 @@
       </c>
       <c r="H75" s="51" t="inlineStr">
         <is>
-          <t>Plan 21, sección 4.</t>
+          <t>Rama refactor/R1-servicios-ia, 6 commits (9ac27a4, 72b35c8, f01bbd0, 9306750, 458118e, b899d45). aiController 901 → 152 líneas; cliente único de OpenAI; services/ia/ con 14 módulos. 365 unitarias + 431 de integración en verde; cobertura combinada 73,5 %. Plan 21, «R1 — Resultados».</t>
         </is>
       </c>
       <c r="I75" s="51" t="inlineStr">
         <is>
-          <t>Después del piloto, salvo que la fecha del Sprint 6.3 lo exija antes.</t>
-        </is>
-      </c>
-      <c r="J75" s="51" t="n"/>
+          <t>Falta que Luis la apruebe y la mezcle a main. Se despliega después del piloto (congelamiento).</t>
+        </is>
+      </c>
+      <c r="J75" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
       <c r="K75" s="53" t="n">
-        <v>46292</v>
+        <v>46303</v>
       </c>
       <c r="L75" s="54">
         <f>IF(K75="","",TODAY()-K75)</f>
@@ -5596,10 +5600,14 @@
           <t>Plan 21, sección 4.</t>
         </is>
       </c>
-      <c r="I76" s="51" t="n"/>
+      <c r="I76" s="51" t="inlineStr">
+        <is>
+          <t>Antes de R2, caracterizar también las ramas de error de cada endpoint (lección de R1). suppliersController es hoy el controlador más grande (632 líneas) y conserva el prompt de generateSmartOrder.</t>
+        </is>
+      </c>
       <c r="J76" s="51" t="n"/>
       <c r="K76" s="53" t="n">
-        <v>46292</v>
+        <v>46303</v>
       </c>
       <c r="L76" s="54">
         <f>IF(K76="","",TODAY()-K76)</f>
@@ -5702,10 +5710,14 @@
           <t>Plan 21, sección 4.</t>
         </is>
       </c>
-      <c r="I78" s="51" t="n"/>
+      <c r="I78" s="51" t="inlineStr">
+        <is>
+          <t>Al 8-oct quedan 164 console.* en el backend (authController 24, schedulerService 15, saleController 12, productController 12, app.js 12…). R1 limpió aiController, services/ia, services/inventory y suppliersController. Incluir mover ai_audit.log de la raíz a logs/.</t>
+        </is>
+      </c>
       <c r="J78" s="51" t="n"/>
       <c r="K78" s="53" t="n">
-        <v>46292</v>
+        <v>46303</v>
       </c>
       <c r="L78" s="54">
         <f>IF(K78="","",TODAY()-K78)</f>
@@ -6250,12 +6262,12 @@
       </c>
       <c r="I88" s="51" t="inlineStr">
         <is>
-          <t>Recomendado: sí, antes de tener datos reales en producción.</t>
+          <t>Recomendado: sí, antes de tener datos reales en producción. Ratificado el 8-oct: cargar cualquier módulo que importe config/database.js dispara la auto-migración contra el DATABASE_URL del .env (ocurrió por accidente al comprobar un require; apuntaba a la base local).</t>
         </is>
       </c>
       <c r="J88" s="51" t="n"/>
       <c r="K88" s="53" t="n">
-        <v>46292</v>
+        <v>46303</v>
       </c>
       <c r="L88" s="54">
         <f>IF(K88="","",TODAY()-K88)</f>
@@ -7854,6 +7866,348 @@
       </c>
       <c r="L117" s="54">
         <f>IF(K117="","",TODAY()-K117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="23.85" customHeight="1" s="33">
+      <c r="A118" s="51" t="inlineStr">
+        <is>
+          <t>P21-17</t>
+        </is>
+      </c>
+      <c r="B118" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C118" s="51" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="D118" s="51" t="inlineStr">
+        <is>
+          <t>generar_reporte.js escribía el reporte en Documentacion/ (carpeta que el commit a665b8c eliminó) y npm run test:evidence terminaba en verde sin generarlo</t>
+        </is>
+      </c>
+      <c r="E118" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F118" s="51" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G118" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H118" s="51" t="inlineStr">
+        <is>
+          <t>Corregido en b899d45 (rama refactor/R1-servicios-ia): ruta a docs/ y process.exitCode = 1 si falla. Reporte regenerado: 365 + 431 = 796 pruebas.</t>
+        </is>
+      </c>
+      <c r="I118" s="51" t="inlineStr">
+        <is>
+          <t>Mezclar la rama a main.</t>
+        </is>
+      </c>
+      <c r="J118" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K118" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L118" s="54">
+        <f>IF(K118="","",TODAY()-K118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="23.85" customHeight="1" s="33">
+      <c r="A119" s="51" t="inlineStr">
+        <is>
+          <t>P21-18</t>
+        </is>
+      </c>
+      <c r="B119" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C119" s="51" t="inlineStr">
+        <is>
+          <t>Documentación</t>
+        </is>
+      </c>
+      <c r="D119" s="51" t="inlineStr">
+        <is>
+          <t>El CLAUDE.md del repo todavía cita Documentacion/Reporte_Pruebas_StockPilot.md; hoy el reporte está en docs/</t>
+        </is>
+      </c>
+      <c r="E119" s="51" t="inlineStr">
+        <is>
+          <t>Mantenimiento de docs</t>
+        </is>
+      </c>
+      <c r="F119" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G119" s="51" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="H119" s="51" t="inlineStr">
+        <is>
+          <t>CLAUDE.md (sección «Antes de ejecutar comandos que escriben o regeneran archivos»).</t>
+        </is>
+      </c>
+      <c r="I119" s="51" t="inlineStr">
+        <is>
+          <t>Es un archivo de Luis: pendiente de que lo actualice.</t>
+        </is>
+      </c>
+      <c r="J119" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K119" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L119" s="54">
+        <f>IF(K119="","",TODAY()-K119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="23.85" customHeight="1" s="33">
+      <c r="A120" s="51" t="inlineStr">
+        <is>
+          <t>P21-19</t>
+        </is>
+      </c>
+      <c r="B120" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C120" s="51" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="D120" s="51" t="inlineStr">
+        <is>
+          <t>coverage.include usa utils/**/*.js, que también cuenta 4 archivos de frontend/src/utils (arqueo, menu, pedir, security2FA; 126 sentencias al 100 %) en la cobertura del backend</t>
+        </is>
+      </c>
+      <c r="E120" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F120" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G120" s="51" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="H120" s="51" t="inlineStr">
+        <is>
+          <t>vitest.config.js. Infla cerca de un punto la cobertura combinada (73,5 % reportado).</t>
+        </is>
+      </c>
+      <c r="I120" s="51" t="inlineStr">
+        <is>
+          <t>Acotar el patrón (p. ej. ./utils/**) o documentar que es intencional.</t>
+        </is>
+      </c>
+      <c r="J120" s="51" t="n"/>
+      <c r="K120" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L120" s="54">
+        <f>IF(K120="","",TODAY()-K120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="23.85" customHeight="1" s="33">
+      <c r="A121" s="51" t="inlineStr">
+        <is>
+          <t>P21-20</t>
+        </is>
+      </c>
+      <c r="B121" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C121" s="51" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="D121" s="51" t="inlineStr">
+        <is>
+          <t>Los umbrales de cobertura unitaria (10/15/19/9) están muy por debajo de lo medido (18,3/25,5/35,1/17,1); el plan 21, sección 3, pide subirlos, nunca bajarlos</t>
+        </is>
+      </c>
+      <c r="E121" s="51" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F121" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G121" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H121" s="51" t="inlineStr">
+        <is>
+          <t>vitest.config.js. Medido el 8-oct con npm run test:coverage:combinada.</t>
+        </is>
+      </c>
+      <c r="I121" s="51" t="inlineStr">
+        <is>
+          <t>Propuesta: 17/23/32/15 (un poco por debajo de lo medido). Es configuración de pruebas/CI: lo decide Luis.</t>
+        </is>
+      </c>
+      <c r="J121" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K121" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L121" s="54">
+        <f>IF(K121="","",TODAY()-K121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="23.85" customHeight="1" s="33">
+      <c r="A122" s="51" t="inlineStr">
+        <is>
+          <t>P21-21</t>
+        </is>
+      </c>
+      <c r="B122" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C122" s="51" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="D122" s="51" t="inlineStr">
+        <is>
+          <t>Zonas con poca cobertura combinada: tenderoController 6 %, dashboardController 10 %, auditController 11 %, schedulerService 12 % (correos), storeController 30 %, reportController 40 %</t>
+        </is>
+      </c>
+      <c r="E122" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F122" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G122" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H122" s="51" t="inlineStr">
+        <is>
+          <t>Cobertura combinada del 8-oct (npm run test:coverage:combinada).</t>
+        </is>
+      </c>
+      <c r="I122" s="51" t="inlineStr">
+        <is>
+          <t>Caracterizarlas antes de R2 y R3. El planificador de correos es el de mayor riesgo.</t>
+        </is>
+      </c>
+      <c r="J122" s="51" t="n"/>
+      <c r="K122" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L122" s="54">
+        <f>IF(K122="","",TODAY()-K122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="23.85" customHeight="1" s="33">
+      <c r="A123" s="51" t="inlineStr">
+        <is>
+          <t>P21-22</t>
+        </is>
+      </c>
+      <c r="B123" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C123" s="51" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="D123" s="51" t="inlineStr">
+        <is>
+          <t>Las corridas de integración muestran MaxListenersExceededWarning (11 listeners en un Server, probablemente supertest con isolate:false)</t>
+        </is>
+      </c>
+      <c r="E123" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F123" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G123" s="51" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="H123" s="51" t="inlineStr">
+        <is>
+          <t>Salida de npm run test:integration y de test:evidence (8-oct).</t>
+        </is>
+      </c>
+      <c r="I123" s="51" t="inlineStr">
+        <is>
+          <t>Inofensivo. Ya aparecía antes del cierre de R1; no se verificó si es anterior a R1.</t>
+        </is>
+      </c>
+      <c r="J123" s="51" t="n"/>
+      <c r="K123" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L123" s="54">
+        <f>IF(K123="","",TODAY()-K123)</f>
         <v/>
       </c>
     </row>
@@ -7925,7 +8279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -8285,29 +8639,59 @@
       <c r="A15" s="53" t="n">
         <v>46301</v>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="32" t="inlineStr">
         <is>
           <t>P23-08</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>En progreso</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="32" t="inlineStr">
         <is>
           <t>En progreso</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="32" t="inlineStr">
         <is>
           <t>Agente (Claude Code)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="32" t="inlineStr">
         <is>
           <t>Se consolidó todo en Documentacion/Revision_Documento_Practica_5_v2.docx (24 páginas en Word, 10 tablas): revisión del 26-sep actualizada al 6-oct (pruebas 287 + 407, 28,2 KLOC, escáner, rol «Colaborador»), reglas de alertas, textos de la IA, novedades y correcciones a Plan de Negocio, Intervención y Herramientas. Se retira el borrador anterior «Secciones corregidas sobre la IA».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" s="33">
+      <c r="A16" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>P21-02, P21-17 a P21-22</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>No iniciado / —</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>Por verificar / No iniciado</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>R1 del plan 21 hecha en la rama refactor/R1-servicios-ia (6 commits, sin mezclar a main): aiController 901 → 152 líneas, cliente único de OpenAI, services/ia con 14 módulos. 365 unitarias + 431 de integración en verde (796 en el reporte); cobertura combinada 73,5 %. Hallazgos nuevos P21-17 a P21-22: reporte de pruebas en carpeta inexistente (corregido en la rama), ruta vieja en CLAUDE.md, umbrales de cobertura por subir (decisión de Luis), zonas con poca cobertura.</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -5528,7 +5528,7 @@
       </c>
       <c r="F75" s="51" t="inlineStr">
         <is>
-          <t>Por verificar</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="G75" s="51" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="H75" s="51" t="inlineStr">
         <is>
-          <t>Rama refactor/R1-servicios-ia, 6 commits (9ac27a4, 72b35c8, f01bbd0, 9306750, 458118e, b899d45). aiController 901 → 152 líneas; cliente único de OpenAI; services/ia/ con 14 módulos. 365 unitarias + 431 de integración en verde; cobertura combinada 73,5 %. Plan 21, «R1 — Resultados».</t>
+          <t>Rama refactor/R1-servicios-ia (subida) y merge --no-ff a main local el 8-oct. aiController 901 → 152 líneas; cliente único de OpenAI; services/ia/ con 14 módulos. 365 unitarias + 431 de integración en verde; cobertura combinada 73,5 %. Plan 21, «R1 — Resultados».</t>
         </is>
       </c>
       <c r="I75" s="51" t="inlineStr">
         <is>
-          <t>Falta que Luis la apruebe y la mezcle a main. Se despliega después del piloto (congelamiento).</t>
+          <t>Aprobada por Luis el 8-oct. origin/main NO se actualizó: main local tiene 5 commits previos sin subir (incluye el 2FA en CRUD) y subirlo podría desplegar durante el congelamiento. Se despliega después del piloto.</t>
         </is>
       </c>
       <c r="J75" s="51" t="inlineStr">
@@ -7897,7 +7897,7 @@
       </c>
       <c r="F118" s="51" t="inlineStr">
         <is>
-          <t>Por verificar</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="G118" s="51" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="I118" s="51" t="inlineStr">
         <is>
-          <t>Mezclar la rama a main.</t>
+          <t>Mezclado a main local el 8-oct (commit b899d45). Falta subir main.</t>
         </is>
       </c>
       <c r="J118" s="51" t="inlineStr">
@@ -7956,7 +7956,7 @@
       </c>
       <c r="F119" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="G119" s="51" t="inlineStr">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="H119" s="51" t="inlineStr">
         <is>
-          <t>CLAUDE.md (sección «Antes de ejecutar comandos que escriben o regeneran archivos»).</t>
+          <t>CLAUDE.md del repo; commit 6d7db26.</t>
         </is>
       </c>
       <c r="I119" s="51" t="inlineStr">
         <is>
-          <t>Es un archivo de Luis: pendiente de que lo actualice.</t>
+          <t>Corregido el 8-oct con la aprobación de Luis.</t>
         </is>
       </c>
       <c r="J119" s="51" t="inlineStr">
         <is>
-          <t>Luis</t>
+          <t>Agente (Claude Code)</t>
         </is>
       </c>
       <c r="K119" s="53" t="n">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F121" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="G121" s="51" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H121" s="51" t="inlineStr">
         <is>
-          <t>vitest.config.js. Medido el 8-oct con npm run test:coverage:combinada.</t>
+          <t>vitest.config.js: umbrales unitarios 10/15/19/9 → 17/23/32/15 (commit 91d8537). Medido: 18,3/25,3/34,4/17,0; el control falla con código 1 si no se cumple.</t>
         </is>
       </c>
       <c r="I121" s="51" t="inlineStr">
         <is>
-          <t>Propuesta: 17/23/32/15 (un poco por debajo de lo medido). Es configuración de pruebas/CI: lo decide Luis.</t>
+          <t>Aprobado por Luis el 8-oct. Regla del plan 21, sección 3: los pisos solo suben.</t>
         </is>
       </c>
       <c r="J121" s="51" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -8692,6 +8692,36 @@
       <c r="F16" s="32" t="inlineStr">
         <is>
           <t>R1 del plan 21 hecha en la rama refactor/R1-servicios-ia (6 commits, sin mezclar a main): aiController 901 → 152 líneas, cliente único de OpenAI, services/ia con 14 módulos. 365 unitarias + 431 de integración en verde (796 en el reporte); cobertura combinada 73,5 %. Hallazgos nuevos P21-17 a P21-22: reporte de pruebas en carpeta inexistente (corregido en la rama), ruta vieja en CLAUDE.md, umbrales de cobertura por subir (decisión de Luis), zonas con poca cobertura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" s="33">
+      <c r="A17" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>P21-02, P21-17, P21-18, P21-20</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Por verificar / No iniciado</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Luis aprueba R1 y manda mezclarla (8-oct): merge --no-ff a main local; la rama refactor/R1-servicios-ia se sube como evidencia. Aprueba también subir los umbrales de cobertura (17/23/32/15) y corregir la ruta vieja del CLAUDE.md. origin/main no se actualiza todavía: main local lleva 5 commits previos sin subir (incluido el 2FA en CRUD, ec4d48c) y no se sabe si subir main despliega durante el congelamiento. Regla de Luis: cada plan nuevo debe quedar subido, es la evidencia del desarrollo.</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -5538,12 +5538,12 @@
       </c>
       <c r="H75" s="51" t="inlineStr">
         <is>
-          <t>Rama refactor/R1-servicios-ia (subida) y merge --no-ff a main local el 8-oct. aiController 901 → 152 líneas; cliente único de OpenAI; services/ia/ con 14 módulos. 365 unitarias + 431 de integración en verde; cobertura combinada 73,5 %. Plan 21, «R1 — Resultados».</t>
+          <t>Merge --no-ff a main (f93958e) y main subido a origin el 8-oct, junto con la rama refactor/R1-servicios-ia. aiController 901 → 152 líneas; cliente único de OpenAI; services/ia/ con 14 módulos. 365 unitarias + 431 de integración en verde; cobertura combinada 73,5 %. Plan 21, «R1 — Resultados».</t>
         </is>
       </c>
       <c r="I75" s="51" t="inlineStr">
         <is>
-          <t>Aprobada por Luis el 8-oct. origin/main NO se actualizó: main local tiene 5 commits previos sin subir (incluye el 2FA en CRUD) y subirlo podría desplegar durante el congelamiento. Se despliega después del piloto.</t>
+          <t>Aprobada por Luis el 8-oct. Subir main publicó también 5 commits previos suyos (entre ellos el 2FA en CRUD, ec4d48c). Luis autorizó subir a producción: la visita a las tiendas aún no ocurre. Falta comprobar el despliegue en Render.</t>
         </is>
       </c>
       <c r="J75" s="51" t="inlineStr">
@@ -7912,7 +7912,7 @@
       </c>
       <c r="I118" s="51" t="inlineStr">
         <is>
-          <t>Mezclado a main local el 8-oct (commit b899d45). Falta subir main.</t>
+          <t>Subido a main el 8-oct (commit b899d45).</t>
         </is>
       </c>
       <c r="J118" s="51" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -8722,6 +8722,36 @@
       <c r="F17" s="32" t="inlineStr">
         <is>
           <t>Luis aprueba R1 y manda mezclarla (8-oct): merge --no-ff a main local; la rama refactor/R1-servicios-ia se sube como evidencia. Aprueba también subir los umbrales de cobertura (17/23/32/15) y corregir la ruta vieja del CLAUDE.md. origin/main no se actualiza todavía: main local lleva 5 commits previos sin subir (incluido el 2FA en CRUD, ec4d48c) y no se sabe si subir main despliega durante el congelamiento. Regla de Luis: cada plan nuevo debe quedar subido, es la evidencia del desarrollo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" s="33">
+      <c r="A18" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>P21-02, P21-17, P21-18, P21-20</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>Terminado</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>Luis autoriza subir a producción (8-oct): la visita a las tiendas aún no ocurre. Se sube main a origin con R1 y con 5 commits previos que estaban sin subir (incluido el 2FA en CRUD, ec4d48c). Se corrige lo anotado antes: ya no queda origin/main pendiente. El congelamiento del piloto rige desde su arranque.</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -1697,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="32" min="1" max="1"/>
@@ -8208,6 +8208,352 @@
       </c>
       <c r="L123" s="54">
         <f>IF(K123="","",TODAY()-K123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="23.85" customHeight="1" s="33">
+      <c r="A124" s="51" t="inlineStr">
+        <is>
+          <t>P21-23</t>
+        </is>
+      </c>
+      <c r="B124" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C124" s="51" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D124" s="51" t="inlineStr">
+        <is>
+          <t>El 2FA «obligatorio» del commit ec4d48c solo existía en el navegador: la API aceptaba cualquier escritura de un Administrador sin 2FA</t>
+        </is>
+      </c>
+      <c r="E124" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F124" s="51" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G124" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H124" s="51" t="inlineStr">
+        <is>
+          <t>Rama feat/2fa-politica-servidor (commits de la política en el servidor y del frontend). middleware/twoFactor.js, 18 pruebas de integración. Verificado en el navegador contra stockpilot_test.</t>
+        </is>
+      </c>
+      <c r="I124" s="51" t="inlineStr">
+        <is>
+          <t>Apagada por defecto (REQUIRE_ADMIN_2FA); decisión de Luis del 8-oct: en el piloto se informa, no se exige. Falta mezclar a main.</t>
+        </is>
+      </c>
+      <c r="J124" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K124" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L124" s="54">
+        <f>IF(K124="","",TODAY()-K124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="23.85" customHeight="1" s="33">
+      <c r="A125" s="51" t="inlineStr">
+        <is>
+          <t>P21-24</t>
+        </is>
+      </c>
+      <c r="B125" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C125" s="51" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D125" s="51" t="inlineStr">
+        <is>
+          <t>generate2FA sobrescribía el secreto de un 2FA ya activo sin pedir contraseña ni código (una sesión robada podía cambiar el segundo factor)</t>
+        </is>
+      </c>
+      <c r="E125" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F125" s="51" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G125" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H125" s="51" t="inlineStr">
+        <is>
+          <t>controllers/authController.js: 409 DOS_FACTORES_YA_ACTIVO. Cubierto en politica_dos_factores.test.js.</t>
+        </is>
+      </c>
+      <c r="I125" s="51" t="inlineStr">
+        <is>
+          <t>Falta mezclar a main.</t>
+        </is>
+      </c>
+      <c r="J125" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K125" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L125" s="54">
+        <f>IF(K125="","",TODAY()-K125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="23.85" customHeight="1" s="33">
+      <c r="A126" s="51" t="inlineStr">
+        <is>
+          <t>P21-25</t>
+        </is>
+      </c>
+      <c r="B126" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C126" s="51" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D126" s="51" t="inlineStr">
+        <is>
+          <t>/api/2fa/generate y /api/2fa/disable no tenían limitador de intentos (disable pide la contraseña y se podía adivinar sin límite)</t>
+        </is>
+      </c>
+      <c r="E126" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F126" s="51" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G126" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H126" s="51" t="inlineStr">
+        <is>
+          <t>middleware/rateLimiter.js: twoFactorSetupLimiter (5 fallos / 15 min), aparte de twoFactorLimiter. Cubierto en politica_dos_factores.test.js.</t>
+        </is>
+      </c>
+      <c r="I126" s="51" t="inlineStr">
+        <is>
+          <t>Falta mezclar a main.</t>
+        </is>
+      </c>
+      <c r="J126" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K126" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L126" s="54">
+        <f>IF(K126="","",TODAY()-K126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" ht="23.85" customHeight="1" s="33">
+      <c r="A127" s="51" t="inlineStr">
+        <is>
+          <t>P21-26</t>
+        </is>
+      </c>
+      <c r="B127" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C127" s="51" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D127" s="51" t="inlineStr">
+        <is>
+          <t>Códigos de recuperación del 2FA: si un dueño pierde el celular queda fuera de su cuenta</t>
+        </is>
+      </c>
+      <c r="E127" s="51" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F127" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G127" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H127" s="51" t="inlineStr">
+        <is>
+          <t>Plan 21, revisión del 2FA. Hoy solo existe el procedimiento manual de soporte (docs/Protocolo_Produccion.md, sección 5).</t>
+        </is>
+      </c>
+      <c r="I127" s="51" t="inlineStr">
+        <is>
+          <t>Prerrequisito de encender REQUIRE_ADMIN_2FA. Después del piloto.</t>
+        </is>
+      </c>
+      <c r="J127" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K127" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L127" s="54">
+        <f>IF(K127="","",TODAY()-K127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="23.85" customHeight="1" s="33">
+      <c r="A128" s="51" t="inlineStr">
+        <is>
+          <t>P21-27</t>
+        </is>
+      </c>
+      <c r="B128" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C128" s="51" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D128" s="51" t="inlineStr">
+        <is>
+          <t>El secreto TOTP se guarda en texto plano en Usuarios.two_factor_secret y la ventana de tolerancia de otplib es la de por defecto</t>
+        </is>
+      </c>
+      <c r="E128" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F128" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G128" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H128" s="51" t="inlineStr">
+        <is>
+          <t>models/User.js (set2FASecret); controllers/authController.js (authenticator.check sin options).</t>
+        </is>
+      </c>
+      <c r="I128" s="51" t="inlineStr">
+        <is>
+          <t>Revisar el cifrado en reposo después del piloto.</t>
+        </is>
+      </c>
+      <c r="J128" s="51" t="n"/>
+      <c r="K128" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L128" s="54">
+        <f>IF(K128="","",TODAY()-K128)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" ht="23.85" customHeight="1" s="33">
+      <c r="A129" s="51" t="inlineStr">
+        <is>
+          <t>P21-28</t>
+        </is>
+      </c>
+      <c r="B129" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C129" s="51" t="inlineStr">
+        <is>
+          <t>Refactorización</t>
+        </is>
+      </c>
+      <c r="D129" s="51" t="inlineStr">
+        <is>
+          <t>ProfilePage tiene su propio modal de activación del 2FA, copia del nuevo components/security/Activar2FAModal.jsx</t>
+        </is>
+      </c>
+      <c r="E129" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F129" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G129" s="51" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="H129" s="51" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/ProfilePage.jsx (show2FAModal).</t>
+        </is>
+      </c>
+      <c r="I129" s="51" t="inlineStr">
+        <is>
+          <t>Unificar al tocar el perfil (R3).</t>
+        </is>
+      </c>
+      <c r="J129" s="51" t="n"/>
+      <c r="K129" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L129" s="54">
+        <f>IF(K129="","",TODAY()-K129)</f>
         <v/>
       </c>
     </row>
@@ -8279,7 +8625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -8752,6 +9098,36 @@
       <c r="F18" s="32" t="inlineStr">
         <is>
           <t>Luis autoriza subir a producción (8-oct): la visita a las tiendas aún no ocurre. Se sube main a origin con R1 y con 5 commits previos que estaban sin subir (incluido el 2FA en CRUD, ec4d48c). Se corrige lo anotado antes: ya no queda origin/main pendiente. El congelamiento del piloto rige desde su arranque.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" s="33">
+      <c r="A19" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>P21-23 a P21-28</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>Por verificar / No iniciado</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Revisión del 2FA del commit ec4d48c: era solo frontend. Luis decide que en el piloto el 2FA se informa pero no se exige, y aprueba mover el control al servidor como política apagada por defecto (REQUIRE_ADMIN_2FA). Rama feat/2fa-politica-servidor (política en el servidor, 409 en generate2FA, limitador, aviso en el frontend). Pendiente: mezclar a main, códigos de recuperación antes de encender la política.</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -1697,7 +1697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="32" min="1" max="1"/>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="F91" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Por verificar</t>
         </is>
       </c>
       <c r="G91" s="51" t="inlineStr">
@@ -6422,17 +6422,21 @@
       </c>
       <c r="H91" s="51" t="inlineStr">
         <is>
-          <t>Plan 22, secciones 3.1 y 3.2.</t>
+          <t>Rama feat/panel-interno-metricas (cc0cbc0, df92831). Esquema interno, cuentas del equipo por script (npm run equipo:crear), login con 2FA obligatorio, requireEquipo, bitácora. Probado: 34 de integración + script de punta a punta + navegador real.</t>
         </is>
       </c>
       <c r="I91" s="51" t="inlineStr">
         <is>
-          <t>Antes del arranque del piloto (plan 22, sección 5, C.2).</t>
-        </is>
-      </c>
-      <c r="J91" s="51" t="n"/>
+          <t>Falta mezclar a main y crear las cuentas en producción (docs/Protocolo_Produccion.md, sección 6).</t>
+        </is>
+      </c>
+      <c r="J91" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
       <c r="K91" s="53" t="n">
-        <v>46293</v>
+        <v>46303</v>
       </c>
       <c r="L91" s="54">
         <f>IF(K91="","",TODAY()-K91)</f>
@@ -6467,7 +6471,7 @@
       </c>
       <c r="F92" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Por verificar</t>
         </is>
       </c>
       <c r="G92" s="51" t="inlineStr">
@@ -6477,17 +6481,21 @@
       </c>
       <c r="H92" s="51" t="inlineStr">
         <is>
-          <t>Plan 22, secciones 3.3 y 3.5.</t>
+          <t>Rama feat/panel-interno-metricas (cc0cbc0, df92831, eb0a7f2). Vistas v_tiendas_resumen/v_activacion/v_adopcion_semanal y pantallas Tiendas, Detalle, Embudo y Bitácora. 32 + 30 de integración. Funciona con una sola tienda.</t>
         </is>
       </c>
       <c r="I92" s="51" t="inlineStr">
         <is>
-          <t>Antes del arranque del piloto. Debe excluir las tiendas de prueba (P22-19).</t>
-        </is>
-      </c>
-      <c r="J92" s="51" t="n"/>
+          <t>Excluye las tiendas de prueba. Pendiente que Luis confirme 3 definiciones propuestas (P22-20 y P22-21).</t>
+        </is>
+      </c>
+      <c r="J92" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
       <c r="K92" s="53" t="n">
-        <v>46293</v>
+        <v>46303</v>
       </c>
       <c r="L92" s="54">
         <f>IF(K92="","",TODAY()-K92)</f>
@@ -6577,7 +6585,7 @@
       </c>
       <c r="F94" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="G94" s="51" t="inlineStr">
@@ -6587,17 +6595,17 @@
       </c>
       <c r="H94" s="51" t="inlineStr">
         <is>
-          <t>Plan 22, secciones 3.5 y 3.7; plan 19, 3.5.</t>
+          <t>Hecha la pantalla de embudo (rama feat/panel-interno-metricas).</t>
         </is>
       </c>
       <c r="I94" s="51" t="inlineStr">
         <is>
-          <t>Antes del arranque del piloto.</t>
+          <t>Falta: preguntas del registro (días de apertura, experiencia digital), párrafo de la política de datos (texto legal: lo aprueba Luis) y encuesta de satisfacción.</t>
         </is>
       </c>
       <c r="J94" s="51" t="n"/>
       <c r="K94" s="53" t="n">
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="L94" s="54">
         <f>IF(K94="","",TODAY()-K94)</f>
@@ -7327,7 +7335,7 @@
       </c>
       <c r="F108" s="51" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Por verificar</t>
         </is>
       </c>
       <c r="G108" s="51" t="inlineStr">
@@ -7337,17 +7345,17 @@
       </c>
       <c r="H108" s="51" t="inlineStr">
         <is>
-          <t>Plan 22, sección 3.3.</t>
+          <t>Tienda.es_prueba (migración) y botón «Marcar como tienda de prueba» en el detalle de la tienda, con confirmación y rastro en la bitácora. Las vistas de activación y adopción la excluyen.</t>
         </is>
       </c>
       <c r="I108" s="51" t="inlineStr">
         <is>
-          <t>Antes del arranque del piloto, junto con I2.</t>
+          <t>Antes del arranque: marcar en producción las tiendas del equipo (QA, demostración, admin/admin123).</t>
         </is>
       </c>
       <c r="J108" s="51" t="n"/>
       <c r="K108" s="53" t="n">
-        <v>46293</v>
+        <v>46303</v>
       </c>
       <c r="L108" s="54">
         <f>IF(K108="","",TODAY()-K108)</f>
@@ -8554,6 +8562,301 @@
       </c>
       <c r="L129" s="54">
         <f>IF(K129="","",TODAY()-K129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="23.85" customHeight="1" s="33">
+      <c r="A130" s="51" t="inlineStr">
+        <is>
+          <t>P22-20</t>
+        </is>
+      </c>
+      <c r="B130" s="52" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C130" s="51" t="inlineStr">
+        <is>
+          <t>Panel interno</t>
+        </is>
+      </c>
+      <c r="D130" s="51" t="inlineStr">
+        <is>
+          <t>Confirmar dos definiciones PROPUESTAS del panel: el umbral «regular» de la adopción (50 %) y qué es «con uso en la semana 4» (≥ 1 día con ventas entre los días 22 y 28)</t>
+        </is>
+      </c>
+      <c r="E130" s="51" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F130" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G130" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H130" s="51" t="inlineStr">
+        <is>
+          <t>services/interno/definiciones.js (UMBRAL_ADOPCION_REGULAR, SEMANA_DEL_EMBUDO); plan 22, «I1 e I2 — Resultados».</t>
+        </is>
+      </c>
+      <c r="I130" s="51" t="inlineStr">
+        <is>
+          <t>Fijar ANTES de publicar la convocatoria (documento de intervención, sección 1.6).</t>
+        </is>
+      </c>
+      <c r="J130" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K130" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L130" s="54">
+        <f>IF(K130="","",TODAY()-K130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="23.85" customHeight="1" s="33">
+      <c r="A131" s="51" t="inlineStr">
+        <is>
+          <t>P22-21</t>
+        </is>
+      </c>
+      <c r="B131" s="52" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C131" s="51" t="inlineStr">
+        <is>
+          <t>Panel interno</t>
+        </is>
+      </c>
+      <c r="D131" s="51" t="inlineStr">
+        <is>
+          <t>Confirmar qué cuenta como «productos cargados» en la activación: los que tiene la tienda (hoy) o solo los cargados en sus primeros 7 días</t>
+        </is>
+      </c>
+      <c r="E131" s="51" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F131" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G131" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H131" s="51" t="inlineStr">
+        <is>
+          <t>interno.v_activacion expone ambos (productos_cargados y productos_primeros_7d); el cambio es una línea en services/interno/definiciones.js.</t>
+        </is>
+      </c>
+      <c r="I131" s="51" t="inlineStr">
+        <is>
+          <t>La decisión del 28-sep dice «carga al menos 20 productos» sin ventana.</t>
+        </is>
+      </c>
+      <c r="J131" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K131" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L131" s="54">
+        <f>IF(K131="","",TODAY()-K131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" ht="23.85" customHeight="1" s="33">
+      <c r="A132" s="51" t="inlineStr">
+        <is>
+          <t>P22-22</t>
+        </is>
+      </c>
+      <c r="B132" s="52" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C132" s="51" t="inlineStr">
+        <is>
+          <t>Panel interno</t>
+        </is>
+      </c>
+      <c r="D132" s="51" t="inlineStr">
+        <is>
+          <t>Crear las cuentas del equipo en producción y marcar las tiendas de prueba, una vez desplegado el panel</t>
+        </is>
+      </c>
+      <c r="E132" s="51" t="inlineStr">
+        <is>
+          <t>Pendiente del plan</t>
+        </is>
+      </c>
+      <c r="F132" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G132" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H132" s="51" t="inlineStr">
+        <is>
+          <t>docs/Protocolo_Produccion.md, sección 6 (npm run equipo:crear con la URL de Neon, copia de seguridad antes).</t>
+        </is>
+      </c>
+      <c r="I132" s="51" t="inlineStr">
+        <is>
+          <t>Una cuenta por integrante. Revisar en los logs de Render que la migración terminó bien.</t>
+        </is>
+      </c>
+      <c r="J132" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K132" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L132" s="54">
+        <f>IF(K132="","",TODAY()-K132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" ht="23.85" customHeight="1" s="33">
+      <c r="A133" s="51" t="inlineStr">
+        <is>
+          <t>P22-23</t>
+        </is>
+      </c>
+      <c r="B133" s="52" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C133" s="51" t="inlineStr">
+        <is>
+          <t>Panel interno</t>
+        </is>
+      </c>
+      <c r="D133" s="51" t="inlineStr">
+        <is>
+          <t>Aprobar y publicar el párrafo de la política de datos (plan 22, 3.7) que informa las métricas agregadas y que cada consulta del equipo queda registrada</t>
+        </is>
+      </c>
+      <c r="E133" s="51" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F133" s="51" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G133" s="51" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H133" s="51" t="inlineStr">
+        <is>
+          <t>frontend/src/pages/PoliticaDatosPage.jsx. Es un texto legal: no se modificó sin el visto bueno de Luis.</t>
+        </is>
+      </c>
+      <c r="I133" s="51" t="inlineStr">
+        <is>
+          <t>Antes de la convocatoria.</t>
+        </is>
+      </c>
+      <c r="J133" s="51" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K133" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L133" s="54">
+        <f>IF(K133="","",TODAY()-K133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" ht="23.85" customHeight="1" s="33">
+      <c r="A134" s="51" t="inlineStr">
+        <is>
+          <t>P21-29</t>
+        </is>
+      </c>
+      <c r="B134" s="52" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C134" s="51" t="inlineStr">
+        <is>
+          <t>Pruebas</t>
+        </is>
+      </c>
+      <c r="D134" s="51" t="inlineStr">
+        <is>
+          <t>Carrera latente en las pruebas de integración: helpers/db.js cargaba su propia copia de config/database.js y truncaba mientras esa copia migraba (deadlock intermitente)</t>
+        </is>
+      </c>
+      <c r="E134" s="51" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F134" s="51" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G134" s="51" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H134" s="51" t="inlineStr">
+        <is>
+          <t>Corregido en la rama feat/panel-interno-metricas: el helper espera su migración. 60 corridas seguidas sin fallos.</t>
+        </is>
+      </c>
+      <c r="I134" s="51" t="inlineStr">
+        <is>
+          <t>Falta mezclar a main.</t>
+        </is>
+      </c>
+      <c r="J134" s="51" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K134" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="L134" s="54">
+        <f>IF(K134="","",TODAY()-K134)</f>
         <v/>
       </c>
     </row>
@@ -8625,7 +8928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="32" min="1" max="1"/>
@@ -9128,6 +9431,36 @@
       <c r="F19" s="32" t="inlineStr">
         <is>
           <t>Revisión del 2FA del commit ec4d48c: era solo frontend. Luis decide que en el piloto el 2FA se informa pero no se exige, y aprueba mover el control al servidor como política apagada por defecto (REQUIRE_ADMIN_2FA). Rama feat/2fa-politica-servidor (política en el servidor, 409 en generate2FA, limitador, aviso en el frontend). Pendiente: mezclar a main, códigos de recuperación antes de encender la política.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" s="33">
+      <c r="A20" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>P22-02, P22-03, P22-05, P22-19 a P22-23, P21-29</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>Por verificar / Parcial / No iniciado</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>Luis pide implementar las métricas de la pantalla del superusuario para medir las tiendas del piloto, «o al menos la única que acepte usarla». Implementados I1, I2 y la pantalla de embudo en la rama feat/panel-interno-metricas (esquema interno, cuentas del equipo con 2FA por script, vistas, Tiendas/Detalle/Embudo/Bitácora); funciona con una sola tienda. Pendientes de Luis: 3 definiciones propuestas (P22-20, P22-21), el párrafo legal de la política de datos (P22-23) y crear las cuentas en producción (P22-22). Queda de I4: preguntas del registro y encuesta.</t>
         </is>
       </c>
     </row>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$155</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$156</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L155"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -8836,7 +8836,7 @@
       </c>
       <c r="I132" s="53" t="inlineStr">
         <is>
-          <t>Una cuenta por integrante. Revisar en los logs de Render que la migración terminó bien.</t>
+          <t>Una cuenta por integrante. Revisar en los logs de Render que la migración terminó bien. Antes de crear las cuentas de producción hay que mezclar fix/equipo-crear-aviso-contrasena (P22-27): con Node 24 el script mostraba la contraseña al teclearla.</t>
         </is>
       </c>
       <c r="J132" s="53" t="inlineStr">
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="K132" s="55" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="L132" s="56">
         <f>IF(K132="","",TODAY()-K132)</f>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="F151" s="53" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Terminado</t>
         </is>
       </c>
       <c r="G151" s="53" t="inlineStr">
@@ -9944,12 +9944,12 @@
       </c>
       <c r="H151" s="53" t="inlineStr">
         <is>
-          <t>Plan 25, fase 1. Hoy la semilla (seed_test_data.js) usa Math.random y no deja alertas de vencimiento, borradores ni proveedor con correo.</t>
+          <t>Hecha el 9-oct-2026 en feat/tienda-demo: database/demoEscenario.js, database/seed_demo.js, npm run demo:sembrar. Pruebas: demo_escenario (23), demo_guardia (7), demo_sembrado (19, integración); suites completas 444 unitarias y 569 de integración en verde; mutaciones detectadas; recorrido manual en el navegador con una base local stockpilot_demo. Resultados en el plan 25, sección 4.</t>
         </is>
       </c>
       <c r="I151" s="53" t="inlineStr">
         <is>
-          <t>Listo para empezar tras el commit de docs (D7). Revisión /review-plan del 9-oct aplicada al plan.</t>
+          <t>No cubierto: quitar await db.migrationReady (intermitente); envío real de correo; celular. Falta el commit/merge a main (con aprobación de Luis).</t>
         </is>
       </c>
       <c r="J151" s="53" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="I152" s="53" t="inlineStr">
         <is>
-          <t>Espera P25-04. Responsable Equipo (el ensayo lo hace una persona que no escribió el guion).</t>
+          <t>Listo para empezar: P25-04 hecha. Debe incluir la plantilla de .env.demo (no se pudo crear .env.demo.example: regla de permisos), el ensayo cronometrado y las notas de «Cosas a tener presentes» del plan 25.</t>
         </is>
       </c>
       <c r="J152" s="53" t="inlineStr">
@@ -10201,8 +10201,67 @@
         <v/>
       </c>
     </row>
+    <row r="156" ht="66.75" customHeight="1" s="35">
+      <c r="A156" s="53" t="inlineStr">
+        <is>
+          <t>P22-27</t>
+        </is>
+      </c>
+      <c r="B156" s="54" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C156" s="53" t="inlineStr">
+        <is>
+          <t>Panel interno</t>
+        </is>
+      </c>
+      <c r="D156" s="53" t="inlineStr">
+        <is>
+          <t>npm run equipo:crear: en Node 24 la contraseña se veía al teclearla y el aviso «Contraseña…» se borraba (la pantalla parecía detenida en «Usuario»)</t>
+        </is>
+      </c>
+      <c r="E156" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F156" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G156" s="53" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="H156" s="53" t="inlineStr">
+        <is>
+          <t>Corregido el 9-oct-2026 en fix/equipo-crear-aviso-contrasena (commit d176576): services/interno/entradaOculta.js + scripts/equipo_crear.js. Prueba: tests/business_logic/entrada_oculta.test.js (readline real en modo terminal; la implementación anterior queda como referencia). Verificado por tubería contra stockpilot_test.</t>
+        </is>
+      </c>
+      <c r="I156" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar en una terminal real de Luis (el defecto se encontró ahí). Aún no está en main; hace falta mezclar la rama antes de crear las cuentas de producción (P22-22).</t>
+        </is>
+      </c>
+      <c r="J156" s="53" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K156" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L156" s="56">
+        <f>IF(K156="","",TODAY()-K156)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L155"/>
+  <autoFilter ref="A4:L156"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11166,14 +11225,64 @@
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="35">
-      <c r="C33" s="34" t="n"/>
-      <c r="D33" s="34" t="n"/>
-      <c r="E33" s="34" t="n"/>
+      <c r="A33" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B33" s="34" t="inlineStr">
+        <is>
+          <t>P25-04, P25-05</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="D33" s="34" t="inlineStr">
+        <is>
+          <t>Terminado / No iniciado</t>
+        </is>
+      </c>
+      <c r="E33" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>Fase 1 del plan 25 hecha en feat/tienda-demo (escenario puro, siembra con guardia _demo, 49 pruebas nuevas entre unitarias e integración, mutaciones y recorrido manual en el navegador). Suites completas: 444 unitarias y 569 de integración en verde. Ajuste: los pedidos de la demo llevan productos distintos de los que /pedir sugiere. Sin push.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="35">
-      <c r="C34" s="34" t="n"/>
-      <c r="D34" s="34" t="n"/>
-      <c r="E34" s="34" t="n"/>
+      <c r="A34" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B34" s="34" t="inlineStr">
+        <is>
+          <t>P22-27, P22-22</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="34" t="inlineStr">
+        <is>
+          <t>Por verificar / No iniciado</t>
+        </is>
+      </c>
+      <c r="E34" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F34" s="34" t="inlineStr">
+        <is>
+          <t>Luis ejecutó npm run equipo:crear y la pantalla parecía detenida en «Usuario». Causa: en Node 24 rl._writeToOutput no existe, así que el eco no se silenciaba y el aviso de la contraseña se borraba. Corregido en fix/equipo-crear-aviso-contrasena (d176576, sin push) con una prueba de readline real; verificado por tubería, falta confirmarlo en la terminal de Luis. P22-22 espera esa mezcla.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="35">
       <c r="C35" s="34" t="n"/>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$160</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L156"/>
+  <dimension ref="A1:L160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -10260,8 +10260,240 @@
         <v/>
       </c>
     </row>
+    <row r="157" ht="66.75" customHeight="1" s="35">
+      <c r="A157" s="53" t="inlineStr">
+        <is>
+          <t>P17-04</t>
+        </is>
+      </c>
+      <c r="B157" s="54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C157" s="53" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="D157" s="53" t="inlineStr">
+        <is>
+          <t>La campanita mostraba solo 5 alertas (críticas primero) y «+9»; las tarjetas del Monitor contaban por tipo (4/3/5) pero sus filtros por severidad (6/5/1); «Productos Agotados» del Dashboard contaba alertas de stock crítico</t>
+        </is>
+      </c>
+      <c r="E157" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F157" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G157" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H157" s="53" t="inlineStr">
+        <is>
+          <t>Corregido el 9-oct-2026 en fix/campanita-alertas-coherentes (commit 960d7c6, sin push): frontend/src/utils/alertas.js (regla única = Alert.getStats), NotificationCenter.jsx, AlertasPage.jsx, DashboardPage.jsx. Pruebas: alertas_utils.test.js (12) y alertas_conteo_coherente.test.js (3, compara con /api/alertas/stats). Verificado en el navegador con la demostración (campanita 12, Monitor 12/4/3/5). Mezclado en local en feat/tienda-demo el 9-oct.</t>
+        </is>
+      </c>
+      <c r="I157" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar por Luis en su pantalla. No cambia la API ni el contrato [A1]. Falta mezclar a main.</t>
+        </is>
+      </c>
+      <c r="J157" s="53" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K157" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L157" s="56">
+        <f>IF(K157="","",TODAY()-K157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" ht="66.75" customHeight="1" s="35">
+      <c r="A158" s="53" t="inlineStr">
+        <is>
+          <t>P17-05</t>
+        </is>
+      </c>
+      <c r="B158" s="54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C158" s="53" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="D158" s="53" t="inlineStr">
+        <is>
+          <t>Regla única de alertas por severidad en API y web: críticas = stock crítico + vencimiento crítico; advertencias = stock bajo + próximas a vencer; info = sobrestock y avisos; por producto distinto; separadores por tipo en el Monitor</t>
+        </is>
+      </c>
+      <c r="E158" s="53" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F158" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G158" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H158" s="53" t="inlineStr">
+        <is>
+          <t>Decidida e implementada el 9-oct-2026 (decisión de Luis): models/Alert.js (getStats por severidad), frontend/src/utils/alertas.js (regla única y seccionesDeAlertas), AlertasPage.jsx (separadores), DashboardPage.jsx («Productos en Estado Crítico»), contrato [A1] y plan 17 actualizados. Pruebas: alertas_utils (20) y alertas_conteo_coherente (5, compara servidor y frontend). Verificado en el navegador: Monitor 12/6/5/1, menú 6, Dashboard 6, campanita 12. Commits en feat/tienda-demo.</t>
+        </is>
+      </c>
+      <c r="I158" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar por Luis en su pantalla (reiniciar npm run demo:servidor para tomar la regla del servidor). Cambia el significado de GET /api/alertas/stats: ver P17-07.</t>
+        </is>
+      </c>
+      <c r="J158" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K158" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L158" s="56">
+        <f>IF(K158="","",TODAY()-K158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" ht="66.75" customHeight="1" s="35">
+      <c r="A159" s="53" t="inlineStr">
+        <is>
+          <t>P17-06</t>
+        </is>
+      </c>
+      <c r="B159" s="54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C159" s="53" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="D159" s="53" t="inlineStr">
+        <is>
+          <t>Detalles de la campanita fuera de lo corregido: «Mensajes para ti» limitado a 5 sin ver más; sobrestock navega a /analisis-detallado (contiene «stock»); descuadre_caja y solicitud_producto sin ícono propio (el frontend espera discrepancia_caja)</t>
+        </is>
+      </c>
+      <c r="E159" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F159" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G159" s="53" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="H159" s="53" t="inlineStr">
+        <is>
+          <t>frontend/src/components/NotificationCenter.jsx (líneas ~126, 339-340 y estilos de tipos); controllers/cashRegisterController.js:72 emite descuadre_caja.</t>
+        </is>
+      </c>
+      <c r="I159" s="53" t="inlineStr">
+        <is>
+          <t>Encontrado al investigar P17-04; no se tocó para no ampliar el alcance.</t>
+        </is>
+      </c>
+      <c r="J159" s="53" t="n"/>
+      <c r="K159" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L159" s="56">
+        <f>IF(K159="","",TODAY()-K159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" ht="66.75" customHeight="1" s="35">
+      <c r="A160" s="53" t="inlineStr">
+        <is>
+          <t>P17-07</t>
+        </is>
+      </c>
+      <c r="B160" s="54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C160" s="53" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="D160" s="53" t="inlineStr">
+        <is>
+          <t>Avisar al equipo de la app del cambio de significado de GET /api/alertas/stats (contrato [A1]): critico/advertencia ahora incluyen vencimientos; los campos son los mismos</t>
+        </is>
+      </c>
+      <c r="E160" s="53" t="inlineStr">
+        <is>
+          <t>Pendiente del plan</t>
+        </is>
+      </c>
+      <c r="F160" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G160" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H160" s="53" t="inlineStr">
+        <is>
+          <t>docs/contrato_api_app_tendero.md [A1] (actualizado el 9-oct-2026); regla en models/Alert.js getStats. Cambio compatible en forma, distinto en significado (paso 3 de la sección 12 del contrato).</t>
+        </is>
+      </c>
+      <c r="I160" s="53" t="inlineStr">
+        <is>
+          <t>La app no va en la visita ni en el piloto, pero su insignia del menú usa este endpoint. Avisar antes de desplegar a producción.</t>
+        </is>
+      </c>
+      <c r="J160" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K160" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L160" s="56">
+        <f>IF(K160="","",TODAY()-K160)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L156"/>
+  <autoFilter ref="A4:L160"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11285,14 +11517,64 @@
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="35">
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
+      <c r="A35" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B35" s="34" t="inlineStr">
+        <is>
+          <t>P17-04, P17-05, P17-06</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="34" t="inlineStr">
+        <is>
+          <t>Por verificar / No iniciado</t>
+        </is>
+      </c>
+      <c r="E35" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F35" s="34" t="inlineStr">
+        <is>
+          <t>Luis notó que la campanita mostraba 5 alertas con «+9», el Dashboard 4 urgentes y los 6 elementos de abajo (tarjetas del Consejero IA, no alertas). Causas: la campanita pedía limit=5 y solo salían críticas; las tarjetas del Monitor contaban por tipo y los filtros por severidad. Corregido solo en web en fix/campanita-alertas-coherentes (960d7c6, sin push; 426 unitarias y 553 de integración en verde). Luis decide después si se adopta la regla única por severidad (P17-05).</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="35">
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="34" t="n"/>
+      <c r="A36" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B36" s="34" t="inlineStr">
+        <is>
+          <t>P17-05, P17-07</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="D36" s="34" t="inlineStr">
+        <is>
+          <t>Por verificar / No iniciado</t>
+        </is>
+      </c>
+      <c r="E36" s="34" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="F36" s="34" t="inlineStr">
+        <is>
+          <t>Luis decide la regla por severidad: todas las críticas juntas (stock y vencimiento), las amarillas juntas, con separadores por tipo en el Monitor; la campanita ya distingue por ícono (caja o calendario). Implementado en API y web (models/Alert.js, utils/alertas.js, Monitor, Dashboard), contrato [A1] y plan 17 actualizados; 20 + 5 pruebas nuevas. Falta avisar al equipo de la app (P17-07) y que Luis lo verifique en su pantalla.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="35">
       <c r="C37" s="34" t="n"/>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$162</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L160"/>
+  <dimension ref="A1:L162"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="F152" s="53" t="inlineStr">
         <is>
-          <t>No iniciado</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="G152" s="53" t="inlineStr">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="H152" s="53" t="inlineStr">
         <is>
-          <t>Plan 25, fase 2. Entregable de plan 22, sección 5, A.2.</t>
+          <t>Guion hecho el 9-oct-2026: docs/guion_demo_tienda.md (preparación, checklist del día, 10 pasos con rótulos exactos, plan B, lo que no se enseña). npm run demo:servidor. Ensayo técnico en el navegador con una base temporal (aprobar, recibir parcial, enviar sin correo, caja, venta, arqueo, cartera). Plan 25, sección 4, «Fase 2 — Resultados».</t>
         </is>
       </c>
       <c r="I152" s="53" t="inlineStr">
         <is>
-          <t>Listo para empezar: P25-04 hecha. Debe incluir la plantilla de .env.demo (no se pudo crear .env.demo.example: regla de permisos), el ensayo cronometrado y las notas de «Cosas a tener presentes» del plan 25.</t>
+          <t>Falta: ensayo cronometrado por otra persona, correo real al buzón, celular, venta fiada/egreso/historial en pantalla, camino PDF / «ya la envié».</t>
         </is>
       </c>
       <c r="J152" s="53" t="inlineStr">
@@ -10492,8 +10492,126 @@
         <v/>
       </c>
     </row>
+    <row r="161" ht="66.75" customHeight="1" s="35">
+      <c r="A161" s="53" t="inlineStr">
+        <is>
+          <t>P25-09</t>
+        </is>
+      </c>
+      <c r="B161" s="54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C161" s="53" t="inlineStr">
+        <is>
+          <t>Demostración</t>
+        </is>
+      </c>
+      <c r="D161" s="53" t="inlineStr">
+        <is>
+          <t>En /pedir, tras aprobar un pedido la lista «Por pedir» vuelve a sugerir los mismos productos (el motor solo descuenta lo que está en borrador, no lo aprobado ni lo enviado que aún no llegó)</t>
+        </is>
+      </c>
+      <c r="E161" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F161" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G161" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H161" s="53" t="inlineStr">
+        <is>
+          <t>Ensayo del 9-oct-2026 (plan 25, fase 2). Frontend: frontend/src/utils/pedir.js (sugerenciasDePedido recibe el snapshot y el resumen de borradores).</t>
+        </is>
+      </c>
+      <c r="I161" s="53" t="inlineStr">
+        <is>
+          <t>El guion avisa cómo explicarlo. Decidir si las órdenes Aprobadas/Enviadas/Parcial también descuentan (y cuánto, según lo pendiente de recibir).</t>
+        </is>
+      </c>
+      <c r="J161" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K161" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L161" s="56">
+        <f>IF(K161="","",TODAY()-K161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" ht="66.75" customHeight="1" s="35">
+      <c r="A162" s="53" t="inlineStr">
+        <is>
+          <t>P25-10</t>
+        </is>
+      </c>
+      <c r="B162" s="54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C162" s="53" t="inlineStr">
+        <is>
+          <t>Demostración</t>
+        </is>
+      </c>
+      <c r="D162" s="53" t="inlineStr">
+        <is>
+          <t>El campo «Mensaje para el proveedor (opcional)» del detalle de la orden no se envía: el frontend manda mensaje_personalizado y el backend nunca lo lee</t>
+        </is>
+      </c>
+      <c r="E162" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F162" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G162" s="53" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="H162" s="53" t="inlineStr">
+        <is>
+          <t>frontend/src/hooks/useProveedoresPage.js:255 lo envía; controllers/suppliersController.js (sendOrderToSupplier) no lo usa (búsqueda en controllers, routes, services y models: sin resultados).</t>
+        </is>
+      </c>
+      <c r="I162" s="53" t="inlineStr">
+        <is>
+          <t>Incluirlo en el correo o quitar el campo. Relacionado con P25-06 (mismo endpoint).</t>
+        </is>
+      </c>
+      <c r="J162" s="53" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K162" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L162" s="56">
+        <f>IF(K162="","",TODAY()-K162)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L160"/>
+  <autoFilter ref="A4:L162"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11577,9 +11695,34 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="35">
-      <c r="C37" s="34" t="n"/>
-      <c r="D37" s="34" t="n"/>
-      <c r="E37" s="34" t="n"/>
+      <c r="A37" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B37" s="34" t="inlineStr">
+        <is>
+          <t>P25-05, P25-09, P25-10</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="D37" s="34" t="inlineStr">
+        <is>
+          <t>Parcial / No iniciado</t>
+        </is>
+      </c>
+      <c r="E37" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F37" s="34" t="inlineStr">
+        <is>
+          <t>Fase 2 del plan 25: guion de la visita (docs/guion_demo_tienda.md) y ensayo técnico en el navegador sobre una base temporal. Hallazgos: «Por pedir» vuelve a sugerir lo ya aprobado (P25-09) y el mensaje opcional al proveedor no se envía (P25-10). Falta el ensayo cronometrado por otra persona, el correo real y el celular.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="35">
       <c r="C38" s="34" t="n"/>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -1759,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L162"/>
+  <dimension ref="A1:L163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -10610,8 +10610,67 @@
         <v/>
       </c>
     </row>
+    <row r="163" ht="66.75" customHeight="1" s="35">
+      <c r="A163" s="53" t="inlineStr">
+        <is>
+          <t>P25-11</t>
+        </is>
+      </c>
+      <c r="B163" s="54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="C163" s="53" t="inlineStr">
+        <is>
+          <t>Demostración</t>
+        </is>
+      </c>
+      <c r="D163" s="53" t="inlineStr">
+        <is>
+          <t>Vista de celular (Galaxy S23, 360×780): corregir lo que se veía mal en las pantallas de la demostración sin cambiar el escritorio</t>
+        </is>
+      </c>
+      <c r="E163" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F163" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G163" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H163" s="53" t="inlineStr">
+        <is>
+          <t>Rama fix/vista-movil-demo (9-oct-2026): 4 archivos con variantes max-sm/max-md de Tailwind (solo aplican bajo 640/768 px): carrito del POS (✕ y total salían de la tarjeta), «Completar Pago» («Transferencia» se salía), detalle de la orden (recuadros desbordados), historial de órdenes (columna Acción siempre visible) y Cartera (se oculta «Cupo asignado», acciones visibles). Escritorio verificado idéntico (posiciones y tamaños de 7 pantallas a 1280 px, antes y después).</t>
+        </is>
+      </c>
+      <c r="I163" s="53" t="inlineStr">
+        <is>
+          <t>Falta: probar en un teléfono real; tablas anchas de Historial Caja, Egresos e Historial de ventas; botón flotante de «subir» que tapa campos; no revisadas: Catálogo (formulario), Perfil, Reportes, Movimientos, Comunicados, Simulador, Auditoría, Aprendizaje, Registro de tendero, Tiendas, panel /interno, Landing y Registro. Sin pruebas automáticas (el frontend no tiene infraestructura).</t>
+        </is>
+      </c>
+      <c r="J163" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K163" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="L163" s="56">
+        <f>IF(K163="","",TODAY()-K163)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L162"/>
+  <autoFilter ref="A4:L163"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11725,9 +11784,34 @@
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="35">
-      <c r="C38" s="34" t="n"/>
-      <c r="D38" s="34" t="n"/>
-      <c r="E38" s="34" t="n"/>
+      <c r="A38" s="55" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B38" s="34" t="inlineStr">
+        <is>
+          <t>P25-11</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="34" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="E38" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F38" s="34" t="inlineStr">
+        <is>
+          <t>Luis pide probar la demostración en la vista de un Samsung Galaxy S23 y corregir lo que se veía mal sin romper el escritorio. Recorrido de las pantallas del guion a 360×780: 5 correcciones solo móviles (rama fix/vista-movil-demo, sin push a main) y comparación de 7 pantallas de escritorio antes y después sin diferencias de posición ni tamaño. Pendiente: teléfono real y las pantallas no revisadas (P25-11).</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="35">
       <c r="C39" s="34" t="n"/>

--- a/docs/seguimiento_planes.xlsx
+++ b/docs/seguimiento_planes.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leyenda" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$163</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Pendientes'!$A$4:$L$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="34" customWidth="1" style="34" min="1" max="1"/>
@@ -1737,6 +1737,34 @@
       </c>
       <c r="J27" s="40">
         <f>COUNTIF(Pendientes!$B$5:$B$308,E27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" s="42" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F28" s="40" t="inlineStr">
+        <is>
+          <t>Dispositivos de confianza para el 2FA</t>
+        </is>
+      </c>
+      <c r="G28" s="40">
+        <f>COUNTIFS(Pendientes!$B$5:$B$308,E28,Pendientes!$F$5:$F$308,"&lt;&gt;Terminado",Pendientes!$F$5:$F$308,"&lt;&gt;Descartado")-COUNTIFS(Pendientes!$B$5:$B$308,E28,Pendientes!$F$5:$F$308,"")</f>
+        <v/>
+      </c>
+      <c r="H28" s="40">
+        <f>COUNTIFS(Pendientes!$B$5:$B$308,E28,Pendientes!$F$5:$F$308,"Terminado")</f>
+        <v/>
+      </c>
+      <c r="I28" s="40">
+        <f>COUNTIFS(Pendientes!$B$5:$B$308,E28,Pendientes!$F$5:$F$308,"Descartado")</f>
+        <v/>
+      </c>
+      <c r="J28" s="40">
+        <f>COUNTIF(Pendientes!$B$5:$B$308,E28)</f>
         <v/>
       </c>
     </row>
@@ -1759,7 +1787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:L163"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8" customWidth="1" style="34" min="1" max="1"/>
@@ -1779,14 +1807,14 @@
     <row r="1" ht="17.25" customHeight="1" s="35">
       <c r="A1" s="36" t="inlineStr">
         <is>
-          <t>StockPilot · Seguimiento de pendientes de los planes 02 a 25</t>
+          <t>StockPilot · Seguimiento de pendientes de los planes 02 a 26</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" s="35">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>Revisado contra el código y el historial de git (main y origin/main) el 09-10-2026. Cambie el Estado con la lista desplegable y anote la fecha, quién y qué en la Bitácora. Los planes 01 y 03 no tienen pendientes.</t>
+          <t>Revisado contra el código y el historial de git (main y origin/main) el 10-10-2026. Cambie el Estado con la lista desplegable y anote la fecha, quién y qué en la Bitácora. Los planes 01 y 03 no tienen pendientes.</t>
         </is>
       </c>
     </row>
@@ -10669,8 +10697,421 @@
         <v/>
       </c>
     </row>
+    <row r="164" ht="66.75" customHeight="1" s="35">
+      <c r="A164" s="53" t="inlineStr">
+        <is>
+          <t>P17-08</t>
+        </is>
+      </c>
+      <c r="B164" s="54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C164" s="53" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="D164" s="53" t="inlineStr">
+        <is>
+          <t>Las alertas de la tienda quedaban desactualizadas hasta que alguien abría el Monitor: al ingresar a la app no se recalculaban</t>
+        </is>
+      </c>
+      <c r="E164" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F164" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G164" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H164" s="53" t="inlineStr">
+        <is>
+          <t>Corregido el 10-oct-2026 en fix/alertas-al-ingresar (commit f6b4069), mezclado a main (dd26501, c346f80) y subido: services/alertas/refrescoAlEntrar.js, llamado desde authController.js en el login y en verify2FA. Espera como máximo 3 s y nunca rompe el inicio de sesión. Pruebas: tests/business_logic/refresco_alertas_al_entrar.test.js y tests/integration/login_refresca_alertas.test.js. Unitarias 476 en verde; integración completa sobre la rama: 53 archivos y 584 pruebas en verde (corrida de Luis).</t>
+        </is>
+      </c>
+      <c r="I164" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar por Luis en producción tras el despliegue de Render (ingresar y ver la campanita y el Monitor al día). No cambia la API ni el contrato [A1].</t>
+        </is>
+      </c>
+      <c r="J164" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K164" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L164" s="56">
+        <f>IF(K164="","",TODAY()-K164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" ht="66.75" customHeight="1" s="35">
+      <c r="A165" s="53" t="inlineStr">
+        <is>
+          <t>P17-09</t>
+        </is>
+      </c>
+      <c r="B165" s="54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C165" s="53" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="D165" s="53" t="inlineStr">
+        <is>
+          <t>La carga masiva de productos no recalculaba las alertas de la tienda</t>
+        </is>
+      </c>
+      <c r="E165" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F165" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="G165" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H165" s="53" t="inlineStr">
+        <is>
+          <t>Corregido el 10-oct-2026 en fix/alertas-al-ingresar (commit 554c8b2): controllers/productController.js recalcula las alertas al terminar la carga. Prueba: tests/integration/carga_masiva_alertas.test.js (dentro de las 584 de la integración completa en verde). Mezclado a main (dd26501, c346f80).</t>
+        </is>
+      </c>
+      <c r="I165" s="53" t="inlineStr">
+        <is>
+          <t>Por verificar por Luis con una carga masiva real en la tienda de demostración o en producción.</t>
+        </is>
+      </c>
+      <c r="J165" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K165" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L165" s="56">
+        <f>IF(K165="","",TODAY()-K165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="66.75" customHeight="1" s="35">
+      <c r="A166" s="53" t="inlineStr">
+        <is>
+          <t>P17-10</t>
+        </is>
+      </c>
+      <c r="B166" s="54" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C166" s="53" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="D166" s="53" t="inlineStr">
+        <is>
+          <t>Las alertas por vencimiento no se recalculan por el solo paso del tiempo: no hay tarea periódica, solo se refrescan al ocurrir un evento (ingreso a la app, carga masiva, etc.)</t>
+        </is>
+      </c>
+      <c r="E166" s="53" t="inlineStr">
+        <is>
+          <t>Observación / defecto</t>
+        </is>
+      </c>
+      <c r="F166" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G166" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H166" s="53" t="inlineStr">
+        <is>
+          <t>Detectado el 10-oct-2026 al corregir P17-08 y P17-09. Hoy el recálculo depende de que alguien ingrese o cargue productos; un lote que pasa a «por vencer» solo porque pasan los días no genera alerta hasta el siguiente refresco. A confirmar contra el código antes de implementar.</t>
+        </is>
+      </c>
+      <c r="I166" s="53" t="inlineStr">
+        <is>
+          <t>Decidir si se resuelve con una tarea periódica (cron o planificador del hospedaje) o con el refresco al ingresar que ya existe. Una tarea periódica añade infraestructura y puede tocar producción: decide Luis.</t>
+        </is>
+      </c>
+      <c r="J166" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K166" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L166" s="56">
+        <f>IF(K166="","",TODAY()-K166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" ht="66.75" customHeight="1" s="35">
+      <c r="A167" s="53" t="inlineStr">
+        <is>
+          <t>P26-01</t>
+        </is>
+      </c>
+      <c r="B167" s="54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C167" s="53" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D167" s="53" t="inlineStr">
+        <is>
+          <t>Plan 26 (dispositivos de confianza para el 2FA): decisiones D1 a D7 (roles, canal de la app, número de dispositivos, aviso por correo, señal del navegador, qué hace cerrar sesión, fecha)</t>
+        </is>
+      </c>
+      <c r="E167" s="53" t="inlineStr">
+        <is>
+          <t>Decisión pendiente</t>
+        </is>
+      </c>
+      <c r="F167" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G167" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H167" s="53" t="inlineStr">
+        <is>
+          <t>docs/planes/26_dispositivos_de_confianza_2fa.md (propuesta sin implementar, mezclada a main el 10-oct-2026, c346f80). Ya decididas por Luis: máximo 15 días, pedir 2FA desde otro dispositivo, priorizar las vulnerabilidades.</t>
+        </is>
+      </c>
+      <c r="I167" s="53" t="inlineStr">
+        <is>
+          <t>Recomendación del plan: D7 = después del piloto, junto con los códigos de recuperación (P21-26) y REQUIRE_ADMIN_2FA. Toca autenticación y esquema: alto riesgo, no se empieza sin aprobación.</t>
+        </is>
+      </c>
+      <c r="J167" s="53" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="K167" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L167" s="56">
+        <f>IF(K167="","",TODAY()-K167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" ht="66.75" customHeight="1" s="35">
+      <c r="A168" s="53" t="inlineStr">
+        <is>
+          <t>P26-02</t>
+        </is>
+      </c>
+      <c r="B168" s="54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C168" s="53" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D168" s="53" t="inlineStr">
+        <is>
+          <t>Plan 26, fase 1: tabla dispositivos_confianza (hash del token, rotación, detección de reutilización) y reglas puras con pruebas, sin tocar el login</t>
+        </is>
+      </c>
+      <c r="E168" s="53" t="inlineStr">
+        <is>
+          <t>Trabajo futuro</t>
+        </is>
+      </c>
+      <c r="F168" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G168" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H168" s="53" t="inlineStr">
+        <is>
+          <t>docs/planes/26_dispositivos_de_confianza_2fa.md, sección 5. Migración aditiva e idempotente (skill safe-migrations); archivos nuevos config/migraciones/dispositivosConfianza.js y services/seguridad/dispositivosConfianza.js.</t>
+        </is>
+      </c>
+      <c r="I168" s="53" t="inlineStr">
+        <is>
+          <t>Depende de P26-01. Pruebas primero y mutación de cada defensa (token en claro, sin rotar, sin validar el usuario).</t>
+        </is>
+      </c>
+      <c r="J168" s="53" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K168" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L168" s="56">
+        <f>IF(K168="","",TODAY()-K168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" ht="66.75" customHeight="1" s="35">
+      <c r="A169" s="53" t="inlineStr">
+        <is>
+          <t>P26-03</t>
+        </is>
+      </c>
+      <c r="B169" s="54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C169" s="53" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D169" s="53" t="inlineStr">
+        <is>
+          <t>Plan 26, fase 2: integrar con login y verify2FA; la cookie nunca sustituye la contraseña</t>
+        </is>
+      </c>
+      <c r="E169" s="53" t="inlineStr">
+        <is>
+          <t>Trabajo futuro</t>
+        </is>
+      </c>
+      <c r="F169" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G169" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H169" s="53" t="inlineStr">
+        <is>
+          <t>docs/planes/26_dispositivos_de_confianza_2fa.md, sección 5. Cookie HttpOnly, SameSite=Strict, Secure en producción, máximo 15 días. Prueba obligatoria: cookie válida con contraseña mala = 401 sin sesión, y authLimiter sigue contando.</t>
+        </is>
+      </c>
+      <c r="I169" s="53" t="inlineStr">
+        <is>
+          <t>Depende de P26-02. Parar y preguntar si hay que cambiar el contrato de la app o el orden de findByCredentials.</t>
+        </is>
+      </c>
+      <c r="J169" s="53" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K169" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L169" s="56">
+        <f>IF(K169="","",TODAY()-K169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" ht="66.75" customHeight="1" s="35">
+      <c r="A170" s="53" t="inlineStr">
+        <is>
+          <t>P26-04</t>
+        </is>
+      </c>
+      <c r="B170" s="54" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C170" s="53" t="inlineStr">
+        <is>
+          <t>Seguridad</t>
+        </is>
+      </c>
+      <c r="D170" s="53" t="inlineStr">
+        <is>
+          <t>Plan 26, fase 3: revocación (cambio de contraseña, desactivar 2FA), lista en «Mi perfil», aviso por correo, política de datos y /security-review</t>
+        </is>
+      </c>
+      <c r="E170" s="53" t="inlineStr">
+        <is>
+          <t>Trabajo futuro</t>
+        </is>
+      </c>
+      <c r="F170" s="53" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="G170" s="53" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="H170" s="53" t="inlineStr">
+        <is>
+          <t>docs/planes/26_dispositivos_de_confianza_2fa.md, secciones 3 y 5. Revocar en las tres rutas que llaman a User.updatePassword y en disable2FA; actualizar la política de datos (Ley 1581) y el Protocolo.</t>
+        </is>
+      </c>
+      <c r="I170" s="53" t="inlineStr">
+        <is>
+          <t>Depende de P26-03. Salida: /security-review sin hallazgos altos abiertos.</t>
+        </is>
+      </c>
+      <c r="J170" s="53" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="K170" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L170" s="56">
+        <f>IF(K170="","",TODAY()-K170)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L163"/>
+  <autoFilter ref="A4:L170"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
@@ -11814,19 +12255,94 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="35">
-      <c r="C39" s="34" t="n"/>
-      <c r="D39" s="34" t="n"/>
-      <c r="E39" s="34" t="n"/>
+      <c r="A39" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B39" s="34" t="inlineStr">
+        <is>
+          <t>P17-08, P17-09</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D39" s="34" t="inlineStr">
+        <is>
+          <t>Por verificar</t>
+        </is>
+      </c>
+      <c r="E39" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F39" s="34" t="inlineStr">
+        <is>
+          <t>Luis pide que las alertas se recalculen al ingresar y tras la carga masiva. Rama fix/alertas-al-ingresar (commits f6b4069 y 554c8b2). Integración completa de Luis: 53 archivos y 584 pruebas en verde. Mezclada con las ramas fix/vista-movil-demo y docs/plan-26-dispositivos-de-confianza a main (--no-ff, c346f80) y subida el 10-oct-2026. Pendiente: verificar el despliegue de Render y en pantalla.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="35">
-      <c r="C40" s="34" t="n"/>
-      <c r="D40" s="34" t="n"/>
-      <c r="E40" s="34" t="n"/>
+      <c r="A40" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B40" s="34" t="inlineStr">
+        <is>
+          <t>P17-10</t>
+        </is>
+      </c>
+      <c r="C40" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" s="34" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="E40" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F40" s="34" t="inlineStr">
+        <is>
+          <t>Se anota el recálculo por paso del tiempo de los vencimientos (sin tarea periódica), detectado al corregir P17-08. A decidir por Luis.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="35">
-      <c r="C41" s="34" t="n"/>
-      <c r="D41" s="34" t="n"/>
-      <c r="E41" s="34" t="n"/>
+      <c r="A41" s="55" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B41" s="34" t="inlineStr">
+        <is>
+          <t>P26-01, P26-02, P26-03, P26-04</t>
+        </is>
+      </c>
+      <c r="C41" s="34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D41" s="34" t="inlineStr">
+        <is>
+          <t>No iniciado</t>
+        </is>
+      </c>
+      <c r="E41" s="34" t="inlineStr">
+        <is>
+          <t>Agente (Claude Code)</t>
+        </is>
+      </c>
+      <c r="F41" s="34" t="inlineStr">
+        <is>
+          <t>Plan 26 (dispositivos de confianza para el 2FA): propuesta mezclada a main sin implementar (c346f80). Se agregan sus decisiones y tres fases al seguimiento.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="35">
       <c r="C42" s="34" t="n"/>
